--- a/condo-analyses/outputs/median_condo_fee_by_cbsa_2024.xlsx
+++ b/condo-analyses/outputs/median_condo_fee_by_cbsa_2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="898">
   <si>
     <t xml:space="preserve">GEOID</t>
   </si>
@@ -42,6 +42,12 @@
   </si>
   <si>
     <t xml:space="preserve">med_condo_fee_ann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">average_2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shr_of_val</t>
   </si>
   <si>
     <t xml:space="preserve">10180</t>
@@ -3059,13 +3065,19 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>181969</v>
@@ -3091,13 +3103,19 @@
       <c r="J2" t="n">
         <v>444</v>
       </c>
+      <c r="K2" t="n">
+        <v>112452.376888177</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.394833806351213</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>702209</v>
@@ -3123,13 +3141,19 @@
       <c r="J3" t="n">
         <v>1560</v>
       </c>
+      <c r="K3" t="n">
+        <v>215919.639289188</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.722491018017424</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>146051</v>
@@ -3155,13 +3179,19 @@
       <c r="J4" t="n">
         <v>1248</v>
       </c>
+      <c r="K4" t="n">
+        <v>138606.077536896</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9003934186564</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>132474</v>
@@ -3187,13 +3217,19 @@
       <c r="J5" t="n">
         <v>336</v>
       </c>
+      <c r="K5" t="n">
+        <v>270925.310891001</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.124019420295204</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>913485</v>
@@ -3219,13 +3255,19 @@
       <c r="J6" t="n">
         <v>1956</v>
       </c>
+      <c r="K6" t="n">
+        <v>295652.222256815</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.661588127114073</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>67326</v>
@@ -3245,13 +3287,15 @@
       <c r="J7" t="n">
         <v>336</v>
       </c>
+      <c r="K7"/>
+      <c r="L7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
         <v>102156</v>
@@ -3277,13 +3321,15 @@
       <c r="J8" t="n">
         <v>960</v>
       </c>
+      <c r="K8"/>
+      <c r="L8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
         <v>929919</v>
@@ -3309,13 +3355,19 @@
       <c r="J9" t="n">
         <v>648</v>
       </c>
+      <c r="K9" t="n">
+        <v>235478.161990647</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.275184753661249</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
         <v>148008</v>
@@ -3341,13 +3393,19 @@
       <c r="J10" t="n">
         <v>516</v>
       </c>
+      <c r="K10" t="n">
+        <v>168859.292798391</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.305579865608034</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
         <v>886418</v>
@@ -3373,13 +3431,19 @@
       <c r="J11" t="n">
         <v>2376</v>
       </c>
+      <c r="K11" t="n">
+        <v>290764.212372399</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.817156960484846</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>278330</v>
@@ -3405,13 +3469,19 @@
       <c r="J12" t="n">
         <v>696</v>
       </c>
+      <c r="K12" t="n">
+        <v>172118.818837419</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.404371819828388</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" t="n">
         <v>129227</v>
@@ -3437,13 +3507,19 @@
       <c r="J13" t="n">
         <v>1236</v>
       </c>
+      <c r="K13" t="n">
+        <v>151288.467491546</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.816982299109528</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
         <v>165399</v>
@@ -3469,13 +3545,15 @@
       <c r="J14" t="n">
         <v>3264</v>
       </c>
+      <c r="K14"/>
+      <c r="L14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
         <v>407213</v>
@@ -3501,13 +3579,19 @@
       <c r="J15" t="n">
         <v>1392</v>
       </c>
+      <c r="K15" t="n">
+        <v>253661.746165666</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.548762287195991</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C16" t="n">
         <v>146096</v>
@@ -3533,13 +3617,15 @@
       <c r="J16" t="n">
         <v>876</v>
       </c>
+      <c r="K16"/>
+      <c r="L16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" t="n">
         <v>373875</v>
@@ -3565,13 +3651,19 @@
       <c r="J17" t="n">
         <v>1296</v>
       </c>
+      <c r="K17" t="n">
+        <v>319798.441271719</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.405255258545442</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C18" t="n">
         <v>116427</v>
@@ -3597,13 +3689,15 @@
       <c r="J18" t="n">
         <v>780</v>
       </c>
+      <c r="K18"/>
+      <c r="L18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" t="n">
         <v>248992</v>
@@ -3629,13 +3723,19 @@
       <c r="J19" t="n">
         <v>1596</v>
       </c>
+      <c r="K19" t="n">
+        <v>277263.254297394</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.575626223548585</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C20" t="n">
         <v>422333</v>
@@ -3661,13 +3761,19 @@
       <c r="J20" t="n">
         <v>1200</v>
       </c>
+      <c r="K20" t="n">
+        <v>328917.856592442</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.364832731318356</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" t="n">
         <v>70879</v>
@@ -3687,13 +3793,15 @@
       <c r="J21" t="n">
         <v>504</v>
       </c>
+      <c r="K21"/>
+      <c r="L21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" t="n">
         <v>87467</v>
@@ -3713,13 +3821,15 @@
       <c r="J22" t="n">
         <v>396</v>
       </c>
+      <c r="K22"/>
+      <c r="L22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" t="n">
         <v>221801</v>
@@ -3745,13 +3855,19 @@
       <c r="J23" t="n">
         <v>708</v>
       </c>
+      <c r="K23" t="n">
+        <v>242270.950744638</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.292234788291336</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C24" t="n">
         <v>6409047</v>
@@ -3777,13 +3893,19 @@
       <c r="J24" t="n">
         <v>1320</v>
       </c>
+      <c r="K24" t="n">
+        <v>295930.154970389</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.44605119749695</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" t="n">
         <v>372989</v>
@@ -3809,13 +3931,19 @@
       <c r="J25" t="n">
         <v>3468</v>
       </c>
+      <c r="K25" t="n">
+        <v>224167.863460976</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.54705493751727</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C26" t="n">
         <v>74567</v>
@@ -3841,13 +3969,15 @@
       <c r="J26" t="n">
         <v>2172</v>
       </c>
+      <c r="K26"/>
+      <c r="L26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C27" t="n">
         <v>205355</v>
@@ -3873,13 +4003,19 @@
       <c r="J27" t="n">
         <v>540</v>
       </c>
+      <c r="K27" t="n">
+        <v>279431.050768414</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.193249819057346</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C28" t="n">
         <v>636658</v>
@@ -3905,13 +4041,19 @@
       <c r="J28" t="n">
         <v>708</v>
       </c>
+      <c r="K28" t="n">
+        <v>194376.201732663</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.364242121046153</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29" t="n">
         <v>2550637</v>
@@ -3937,13 +4079,19 @@
       <c r="J29" t="n">
         <v>744</v>
       </c>
+      <c r="K29" t="n">
+        <v>386736.775342788</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.192378911816842</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C30" t="n">
         <v>922529</v>
@@ -3969,13 +4117,19 @@
       <c r="J30" t="n">
         <v>1884</v>
       </c>
+      <c r="K30" t="n">
+        <v>227341.513787255</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.828709182328678</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C31" t="n">
         <v>2859024</v>
@@ -4001,13 +4155,19 @@
       <c r="J31" t="n">
         <v>1164</v>
       </c>
+      <c r="K31" t="n">
+        <v>277360.369388317</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.419670626545189</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C32" t="n">
         <v>156840</v>
@@ -4033,13 +4193,19 @@
       <c r="J32" t="n">
         <v>2172</v>
       </c>
+      <c r="K32" t="n">
+        <v>238165.364411357</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.911971396583319</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C33" t="n">
         <v>66486</v>
@@ -4065,13 +4231,19 @@
       <c r="J33" t="n">
         <v>984</v>
       </c>
+      <c r="K33" t="n">
+        <v>296220.104858597</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.33218542018602</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C34" t="n">
         <v>232570</v>
@@ -4097,13 +4269,19 @@
       <c r="J34" t="n">
         <v>3528</v>
       </c>
+      <c r="K34" t="n">
+        <v>498066.696799665</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.708338867599303</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C35" t="n">
         <v>882652</v>
@@ -4129,13 +4307,19 @@
       <c r="J35" t="n">
         <v>672</v>
       </c>
+      <c r="K35" t="n">
+        <v>133228.743147675</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.504395661268931</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C36" t="n">
         <v>102651</v>
@@ -4161,13 +4345,19 @@
       <c r="J36" t="n">
         <v>3432</v>
       </c>
+      <c r="K36" t="n">
+        <v>231560.005782652</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.48212122745469</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C37" t="n">
         <v>398733</v>
@@ -4193,13 +4383,19 @@
       <c r="J37" t="n">
         <v>984</v>
       </c>
+      <c r="K37" t="n">
+        <v>104685.31285047</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.939959936314587</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C38" t="n">
         <v>88635</v>
@@ -4225,13 +4421,19 @@
       <c r="J38" t="n">
         <v>2040</v>
       </c>
+      <c r="K38" t="n">
+        <v>207519.550672159</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.983039907995373</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C39" t="n">
         <v>110979</v>
@@ -4251,13 +4453,15 @@
       <c r="J39" t="n">
         <v>1848</v>
       </c>
+      <c r="K39"/>
+      <c r="L39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C40" t="n">
         <v>234954</v>
@@ -4283,13 +4487,19 @@
       <c r="J40" t="n">
         <v>1644</v>
       </c>
+      <c r="K40" t="n">
+        <v>376985.519502691</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.436091020729051</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C41" t="n">
         <v>264407</v>
@@ -4315,13 +4525,19 @@
       <c r="J41" t="n">
         <v>936</v>
       </c>
+      <c r="K41" t="n">
+        <v>444431.792356683</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.210605995362457</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C42" t="n">
         <v>192531</v>
@@ -4347,13 +4563,19 @@
       <c r="J42" t="n">
         <v>864</v>
       </c>
+      <c r="K42" t="n">
+        <v>286576.050353779</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.301490651062218</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C43" t="n">
         <v>243971</v>
@@ -4379,13 +4601,15 @@
       <c r="J43" t="n">
         <v>5616</v>
       </c>
+      <c r="K43"/>
+      <c r="L43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C44" t="n">
         <v>1192583</v>
@@ -4411,13 +4635,19 @@
       <c r="J44" t="n">
         <v>708</v>
       </c>
+      <c r="K44" t="n">
+        <v>222110.717353171</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.31875994478656</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C45" t="n">
         <v>138774</v>
@@ -4443,13 +4673,19 @@
       <c r="J45" t="n">
         <v>1992</v>
       </c>
+      <c r="K45" t="n">
+        <v>208615.415473263</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.954867115395557</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C46" t="n">
         <v>183318</v>
@@ -4475,13 +4711,19 @@
       <c r="J46" t="n">
         <v>1080</v>
       </c>
+      <c r="K46" t="n">
+        <v>243713.483857103</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.443143310295149</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C47" t="n">
         <v>172069</v>
@@ -4507,13 +4749,19 @@
       <c r="J47" t="n">
         <v>552</v>
       </c>
+      <c r="K47" t="n">
+        <v>154731.016626333</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.356748124607137</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C48" t="n">
         <v>96399</v>
@@ -4533,13 +4781,19 @@
       <c r="J48" t="n">
         <v>540</v>
       </c>
+      <c r="K48" t="n">
+        <v>150214.380013159</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.359486222259611</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C49" t="n">
         <v>844979</v>
@@ -4565,13 +4819,19 @@
       <c r="J49" t="n">
         <v>756</v>
       </c>
+      <c r="K49" t="n">
+        <v>343773.384255643</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.219912312768754</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C50" t="n">
         <v>5025517</v>
@@ -4597,13 +4857,19 @@
       <c r="J50" t="n">
         <v>4632</v>
       </c>
+      <c r="K50" t="n">
+        <v>570496.860231474</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.811923837428414</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C51" t="n">
         <v>330262</v>
@@ -4629,13 +4895,19 @@
       <c r="J51" t="n">
         <v>1236</v>
       </c>
+      <c r="K51" t="n">
+        <v>443475.494742646</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.27870762074853</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C52" t="n">
         <v>197734</v>
@@ -4661,13 +4933,19 @@
       <c r="J52" t="n">
         <v>288</v>
       </c>
+      <c r="K52" t="n">
+        <v>255527.300136907</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.112708113710627</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C53" t="n">
         <v>126984</v>
@@ -4693,13 +4971,19 @@
       <c r="J53" t="n">
         <v>864</v>
       </c>
+      <c r="K53" t="n">
+        <v>519225.243383453</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.166401770909649</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C54" t="n">
         <v>100084</v>
@@ -4725,13 +5009,19 @@
       <c r="J54" t="n">
         <v>3192</v>
       </c>
+      <c r="K54" t="n">
+        <v>258984.999625299</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.23250381474533</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C55" t="n">
         <v>281420</v>
@@ -4757,13 +5047,19 @@
       <c r="J55" t="n">
         <v>636</v>
       </c>
+      <c r="K55" t="n">
+        <v>396411.131822499</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.160439490454264</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C56" t="n">
         <v>972679</v>
@@ -4789,13 +5085,19 @@
       <c r="J56" t="n">
         <v>5088</v>
       </c>
+      <c r="K56" t="n">
+        <v>384729.410086955</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.32248792699524</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C57" t="n">
         <v>70168</v>
@@ -4815,13 +5117,15 @@
       <c r="J57" t="n">
         <v>1452</v>
       </c>
+      <c r="K57"/>
+      <c r="L57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B58" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C58" t="n">
         <v>431874</v>
@@ -4847,13 +5151,19 @@
       <c r="J58" t="n">
         <v>2160</v>
       </c>
+      <c r="K58" t="n">
+        <v>330787.894367128</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.652986411166155</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B59" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C59" t="n">
         <v>116080</v>
@@ -4879,13 +5189,19 @@
       <c r="J59" t="n">
         <v>588</v>
       </c>
+      <c r="K59" t="n">
+        <v>405763.593444576</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.144911965858838</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C60" t="n">
         <v>1160172</v>
@@ -4911,13 +5227,19 @@
       <c r="J60" t="n">
         <v>3444</v>
       </c>
+      <c r="K60" t="n">
+        <v>225023.295962923</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.53050820150082</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C61" t="n">
         <v>183040</v>
@@ -4943,13 +5265,19 @@
       <c r="J61" t="n">
         <v>1020</v>
       </c>
+      <c r="K61" t="n">
+        <v>225684.275336839</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.451958825433285</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C62" t="n">
         <v>229550</v>
@@ -4975,13 +5303,19 @@
       <c r="J62" t="n">
         <v>2652</v>
       </c>
+      <c r="K62" t="n">
+        <v>362338.349772807</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.731912589893631</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C63" t="n">
         <v>400551</v>
@@ -5007,13 +5341,19 @@
       <c r="J63" t="n">
         <v>864</v>
       </c>
+      <c r="K63" t="n">
+        <v>217845.703770092</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.396610988900584</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C64" t="n">
         <v>860959</v>
@@ -5039,13 +5379,19 @@
       <c r="J64" t="n">
         <v>4932</v>
       </c>
+      <c r="K64" t="n">
+        <v>330065.314186454</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.49424970998737</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C65" t="n">
         <v>100842</v>
@@ -5065,13 +5411,19 @@
       <c r="J65" t="n">
         <v>444</v>
       </c>
+      <c r="K65" t="n">
+        <v>209069.593047063</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.212369476368595</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C66" t="n">
         <v>58148</v>
@@ -5097,13 +5449,19 @@
       <c r="J66" t="n">
         <v>1656</v>
       </c>
+      <c r="K66" t="n">
+        <v>286474.263076958</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.578062399816745</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C67" t="n">
         <v>278677</v>
@@ -5129,13 +5487,19 @@
       <c r="J67" t="n">
         <v>2028</v>
       </c>
+      <c r="K67" t="n">
+        <v>153027.659575032</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1.32525061523642</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C68" t="n">
         <v>87049</v>
@@ -5161,13 +5525,15 @@
       <c r="J68" t="n">
         <v>360</v>
       </c>
+      <c r="K68"/>
+      <c r="L68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C69" t="n">
         <v>159285</v>
@@ -5193,13 +5559,15 @@
       <c r="J69" t="n">
         <v>648</v>
       </c>
+      <c r="K69"/>
+      <c r="L69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C70" t="n">
         <v>243252</v>
@@ -5225,13 +5593,19 @@
       <c r="J70" t="n">
         <v>444</v>
       </c>
+      <c r="K70" t="n">
+        <v>162658.94039918</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.272963784782061</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C71" t="n">
         <v>869940</v>
@@ -5257,13 +5631,19 @@
       <c r="J71" t="n">
         <v>1152</v>
       </c>
+      <c r="K71" t="n">
+        <v>424449.046301011</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.271410669911842</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C72" t="n">
         <v>2883370</v>
@@ -5289,13 +5669,19 @@
       <c r="J72" t="n">
         <v>1080</v>
       </c>
+      <c r="K72" t="n">
+        <v>307281.847133546</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.351468858337937</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B73" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C73" t="n">
         <v>226140</v>
@@ -5321,13 +5707,19 @@
       <c r="J73" t="n">
         <v>1392</v>
       </c>
+      <c r="K73" t="n">
+        <v>259142.657098869</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.537155872207067</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C74" t="n">
         <v>588763</v>
@@ -5353,13 +5745,19 @@
       <c r="J74" t="n">
         <v>804</v>
       </c>
+      <c r="K74" t="n">
+        <v>321171.829857409</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.250333287435873</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B75" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C75" t="n">
         <v>101783</v>
@@ -5385,13 +5783,19 @@
       <c r="J75" t="n">
         <v>540</v>
       </c>
+      <c r="K75" t="n">
+        <v>252256.799644463</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.214067569540678</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C76" t="n">
         <v>9406924</v>
@@ -5417,13 +5821,19 @@
       <c r="J76" t="n">
         <v>3024</v>
       </c>
+      <c r="K76" t="n">
+        <v>255991.833602679</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1.18128768306473</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B77" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C77" t="n">
         <v>208334</v>
@@ -5449,13 +5859,19 @@
       <c r="J77" t="n">
         <v>1356</v>
       </c>
+      <c r="K77" t="n">
+        <v>237500.760854594</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.570945539340899</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B78" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C78" t="n">
         <v>76046</v>
@@ -5479,13 +5895,19 @@
       <c r="J78" t="n">
         <v>2904</v>
       </c>
+      <c r="K78" t="n">
+        <v>240912.022899753</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1.20541929167578</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C79" t="n">
         <v>2304804</v>
@@ -5511,13 +5933,19 @@
       <c r="J79" t="n">
         <v>1464</v>
       </c>
+      <c r="K79" t="n">
+        <v>208365.153643999</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.702612684701258</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C80" t="n">
         <v>89918</v>
@@ -5543,13 +5971,19 @@
       <c r="J80" t="n">
         <v>600</v>
       </c>
+      <c r="K80" t="n">
+        <v>225612.267536638</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.26594298552607</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B81" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C81" t="n">
         <v>344003</v>
@@ -5575,13 +6009,19 @@
       <c r="J81" t="n">
         <v>504</v>
       </c>
+      <c r="K81" t="n">
+        <v>215907.627891463</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.233433160709524</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C82" t="n">
         <v>2171877</v>
@@ -5607,13 +6047,19 @@
       <c r="J82" t="n">
         <v>1920</v>
       </c>
+      <c r="K82" t="n">
+        <v>176441.745405444</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1.08817785472936</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C83" t="n">
         <v>65870</v>
@@ -5631,13 +6077,15 @@
       <c r="J83" t="n">
         <v>456</v>
       </c>
+      <c r="K83"/>
+      <c r="L83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C84" t="n">
         <v>188323</v>
@@ -5663,13 +6111,19 @@
       <c r="J84" t="n">
         <v>576</v>
       </c>
+      <c r="K84" t="n">
+        <v>449685.46558318</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.128089530145923</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C85" t="n">
         <v>288771</v>
@@ -5695,13 +6149,19 @@
       <c r="J85" t="n">
         <v>564</v>
       </c>
+      <c r="K85" t="n">
+        <v>206720.95553729</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.272831556207789</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C86" t="n">
         <v>777635</v>
@@ -5727,13 +6187,19 @@
       <c r="J86" t="n">
         <v>864</v>
       </c>
+      <c r="K86" t="n">
+        <v>281299.07252946</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.307146409062375</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C87" t="n">
         <v>871176</v>
@@ -5759,13 +6225,19 @@
       <c r="J87" t="n">
         <v>684</v>
       </c>
+      <c r="K87" t="n">
+        <v>164095.514557344</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.416830406269863</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C88" t="n">
         <v>328206</v>
@@ -5791,13 +6263,19 @@
       <c r="J88" t="n">
         <v>768</v>
       </c>
+      <c r="K88" t="n">
+        <v>168785.027475796</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.455016663199068</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B89" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C89" t="n">
         <v>84741</v>
@@ -5823,13 +6301,19 @@
       <c r="J89" t="n">
         <v>816</v>
       </c>
+      <c r="K89" t="n">
+        <v>219499.171430561</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.371755389636239</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B90" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C90" t="n">
         <v>68920</v>
@@ -5847,13 +6331,15 @@
       <c r="J90" t="n">
         <v>1248</v>
       </c>
+      <c r="K90"/>
+      <c r="L90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B91" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C91" t="n">
         <v>2225377</v>
@@ -5879,13 +6365,19 @@
       <c r="J91" t="n">
         <v>1272</v>
       </c>
+      <c r="K91" t="n">
+        <v>226433.275885136</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.561754890056554</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B92" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C92" t="n">
         <v>157869</v>
@@ -5911,13 +6403,19 @@
       <c r="J92" t="n">
         <v>2088</v>
       </c>
+      <c r="K92" t="n">
+        <v>333990.897636776</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.625166738008158</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B93" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C93" t="n">
         <v>149734</v>
@@ -5943,13 +6441,19 @@
       <c r="J93" t="n">
         <v>288</v>
       </c>
+      <c r="K93" t="n">
+        <v>191808.651975834</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.150149639775522</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C94" t="n">
         <v>448853</v>
@@ -5975,13 +6479,19 @@
       <c r="J94" t="n">
         <v>864</v>
       </c>
+      <c r="K94" t="n">
+        <v>264431.251844283</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.326738989425043</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B95" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C95" t="n">
         <v>98899</v>
@@ -6007,13 +6517,19 @@
       <c r="J95" t="n">
         <v>816</v>
       </c>
+      <c r="K95" t="n">
+        <v>303542.3250712</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.268825772421884</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B96" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C96" t="n">
         <v>310149</v>
@@ -6039,13 +6555,19 @@
       <c r="J96" t="n">
         <v>1596</v>
       </c>
+      <c r="K96" t="n">
+        <v>613399.36137927</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.260189380766763</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B97" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C97" t="n">
         <v>65618</v>
@@ -6065,13 +6587,19 @@
       <c r="J97" t="n">
         <v>1392</v>
       </c>
+      <c r="K97" t="n">
+        <v>206969.355014405</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.672563336684851</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B98" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C98" t="n">
         <v>93875</v>
@@ -6097,13 +6625,15 @@
       <c r="J98" t="n">
         <v>288</v>
       </c>
+      <c r="K98"/>
+      <c r="L98"/>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B99" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C99" t="n">
         <v>8344032</v>
@@ -6129,13 +6659,19 @@
       <c r="J99" t="n">
         <v>900</v>
       </c>
+      <c r="K99" t="n">
+        <v>237132.296279123</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.379534974409656</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B100" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C100" t="n">
         <v>146386</v>
@@ -6161,13 +6697,19 @@
       <c r="J100" t="n">
         <v>516</v>
       </c>
+      <c r="K100" t="n">
+        <v>220739.765832169</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.233759421667739</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B101" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C101" t="n">
         <v>101403</v>
@@ -6193,13 +6735,15 @@
       <c r="J101" t="n">
         <v>1740</v>
       </c>
+      <c r="K101"/>
+      <c r="L101"/>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B102" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C102" t="n">
         <v>261608</v>
@@ -6225,13 +6769,19 @@
       <c r="J102" t="n">
         <v>744</v>
       </c>
+      <c r="K102" t="n">
+        <v>542932.68351453</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.13703356283212</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B103" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C103" t="n">
         <v>381415</v>
@@ -6257,13 +6807,19 @@
       <c r="J103" t="n">
         <v>1416</v>
       </c>
+      <c r="K103" t="n">
+        <v>156611.754083485</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.904146695940313</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B104" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C104" t="n">
         <v>821740</v>
@@ -6289,13 +6845,15 @@
       <c r="J104" t="n">
         <v>1128</v>
       </c>
+      <c r="K104"/>
+      <c r="L104"/>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B105" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C105" t="n">
         <v>159651</v>
@@ -6321,13 +6879,15 @@
       <c r="J105" t="n">
         <v>504</v>
       </c>
+      <c r="K105"/>
+      <c r="L105"/>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B106" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C106" t="n">
         <v>100737</v>
@@ -6353,13 +6913,19 @@
       <c r="J106" t="n">
         <v>1860</v>
       </c>
+      <c r="K106" t="n">
+        <v>111338.710382038</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1.67057799898863</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B107" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C107" t="n">
         <v>739516</v>
@@ -6385,13 +6951,19 @@
       <c r="J107" t="n">
         <v>2040</v>
       </c>
+      <c r="K107" t="n">
+        <v>340138.575669667</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.599755554330653</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B108" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C108" t="n">
         <v>3050512</v>
@@ -6417,13 +6989,19 @@
       <c r="J108" t="n">
         <v>1368</v>
       </c>
+      <c r="K108" t="n">
+        <v>347019.921749455</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.394213678887198</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B109" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C109" t="n">
         <v>753913</v>
@@ -6449,13 +7027,19 @@
       <c r="J109" t="n">
         <v>1620</v>
       </c>
+      <c r="K109" t="n">
+        <v>207537.070960102</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.780583436253388</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C110" t="n">
         <v>4400578</v>
@@ -6481,13 +7065,19 @@
       <c r="J110" t="n">
         <v>1620</v>
       </c>
+      <c r="K110" t="n">
+        <v>257624.381481252</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.628822470406548</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B111" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C111" t="n">
         <v>154766</v>
@@ -6513,13 +7103,15 @@
       <c r="J111" t="n">
         <v>468</v>
       </c>
+      <c r="K111"/>
+      <c r="L111"/>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B112" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C112" t="n">
         <v>192690</v>
@@ -6545,13 +7137,19 @@
       <c r="J112" t="n">
         <v>552</v>
       </c>
+      <c r="K112" t="n">
+        <v>185679.148883254</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.297287015434926</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B113" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C113" t="n">
         <v>78132</v>
@@ -6577,13 +7175,15 @@
       <c r="J113" t="n">
         <v>1620</v>
       </c>
+      <c r="K113"/>
+      <c r="L113"/>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B114" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C114" t="n">
         <v>99242</v>
@@ -6609,13 +7209,19 @@
       <c r="J114" t="n">
         <v>996</v>
       </c>
+      <c r="K114" t="n">
+        <v>234818.002875105</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.424158279094875</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C115" t="n">
         <v>281815</v>
@@ -6641,13 +7247,19 @@
       <c r="J115" t="n">
         <v>3780</v>
       </c>
+      <c r="K115" t="n">
+        <v>275039.481307757</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1.37434814159293</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C116" t="n">
         <v>620522</v>
@@ -6673,13 +7285,19 @@
       <c r="J116" t="n">
         <v>1044</v>
       </c>
+      <c r="K116" t="n">
+        <v>292808.86136428</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.35654658644404</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B117" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C117" t="n">
         <v>166523</v>
@@ -6705,13 +7323,19 @@
       <c r="J117" t="n">
         <v>1344</v>
       </c>
+      <c r="K117" t="n">
+        <v>188192.053278862</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.714164055592968</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B118" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C118" t="n">
         <v>176153</v>
@@ -6737,13 +7361,19 @@
       <c r="J118" t="n">
         <v>2160</v>
       </c>
+      <c r="K118" t="n">
+        <v>236659.999029756</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.912701769988776</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B119" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C119" t="n">
         <v>181724</v>
@@ -6769,13 +7399,19 @@
       <c r="J119" t="n">
         <v>2328</v>
       </c>
+      <c r="K119" t="n">
+        <v>237227.745851075</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.981335463795812</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B120" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C120" t="n">
         <v>127744</v>
@@ -6801,13 +7437,19 @@
       <c r="J120" t="n">
         <v>288</v>
       </c>
+      <c r="K120" t="n">
+        <v>201312.789161242</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.143060955640193</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B121" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C121" t="n">
         <v>81115</v>
@@ -6829,13 +7471,15 @@
       <c r="J121" t="n">
         <v>1080</v>
       </c>
+      <c r="K121"/>
+      <c r="L121"/>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B122" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C122" t="n">
         <v>877840</v>
@@ -6861,13 +7505,19 @@
       <c r="J122" t="n">
         <v>684</v>
       </c>
+      <c r="K122" t="n">
+        <v>173957.984942289</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.39319839225944</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C123" t="n">
         <v>267750</v>
@@ -6893,13 +7543,19 @@
       <c r="J123" t="n">
         <v>528</v>
       </c>
+      <c r="K123" t="n">
+        <v>251521.81090427</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.209922152715797</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B124" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C124" t="n">
         <v>382396</v>
@@ -6925,13 +7581,19 @@
       <c r="J124" t="n">
         <v>528</v>
       </c>
+      <c r="K124" t="n">
+        <v>283099.746015737</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.186506702118571</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C125" t="n">
         <v>267793</v>
@@ -6957,13 +7619,19 @@
       <c r="J125" t="n">
         <v>1560</v>
       </c>
+      <c r="K125" t="n">
+        <v>181887.33842426</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.85767377405965</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B126" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C126" t="n">
         <v>69025</v>
@@ -6983,13 +7651,19 @@
       <c r="J126" t="n">
         <v>3144</v>
       </c>
+      <c r="K126" t="n">
+        <v>212714.175856326</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1.47803971566218</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C127" t="n">
         <v>67503</v>
@@ -7009,13 +7683,19 @@
       <c r="J127" t="n">
         <v>888</v>
       </c>
+      <c r="K127" t="n">
+        <v>196497.740938618</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.451913592369183</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B128" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C128" t="n">
         <v>120817</v>
@@ -7035,13 +7715,15 @@
       <c r="J128" t="n">
         <v>720</v>
       </c>
+      <c r="K128"/>
+      <c r="L128"/>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C129" t="n">
         <v>393812</v>
@@ -7067,13 +7749,19 @@
       <c r="J129" t="n">
         <v>444</v>
       </c>
+      <c r="K129" t="n">
+        <v>147481.104189928</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.301055516527874</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B130" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C130" t="n">
         <v>605547</v>
@@ -7099,13 +7787,19 @@
       <c r="J130" t="n">
         <v>504</v>
       </c>
+      <c r="K130" t="n">
+        <v>260908.220543471</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.193171376106958</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B131" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C131" t="n">
         <v>75016</v>
@@ -7125,13 +7819,19 @@
       <c r="J131" t="n">
         <v>1392</v>
       </c>
+      <c r="K131" t="n">
+        <v>229298.599547056</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.607068688055523</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B132" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C132" t="n">
         <v>145161</v>
@@ -7157,13 +7857,19 @@
       <c r="J132" t="n">
         <v>720</v>
       </c>
+      <c r="K132" t="n">
+        <v>395967.360254556</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.181833169162512</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C133" t="n">
         <v>402279</v>
@@ -7189,13 +7895,19 @@
       <c r="J133" t="n">
         <v>1620</v>
       </c>
+      <c r="K133" t="n">
+        <v>229855.537374529</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.704790503854755</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B134" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C134" t="n">
         <v>156287</v>
@@ -7221,13 +7933,19 @@
       <c r="J134" t="n">
         <v>552</v>
       </c>
+      <c r="K134" t="n">
+        <v>221449.677465729</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.249266563093291</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B135" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C135" t="n">
         <v>104269</v>
@@ -7253,13 +7971,19 @@
       <c r="J135" t="n">
         <v>1536</v>
       </c>
+      <c r="K135" t="n">
+        <v>242784.883863493</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.632658827665574</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B136" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C136" t="n">
         <v>65587</v>
@@ -7279,13 +8003,19 @@
       <c r="J136" t="n">
         <v>732</v>
       </c>
+      <c r="K136" t="n">
+        <v>306114.833353486</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.239125948906476</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B137" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C137" t="n">
         <v>374574</v>
@@ -7311,13 +8041,19 @@
       <c r="J137" t="n">
         <v>1044</v>
       </c>
+      <c r="K137" t="n">
+        <v>371197.928792651</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.281251569316588</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C138" t="n">
         <v>232848</v>
@@ -7343,13 +8079,19 @@
       <c r="J138" t="n">
         <v>684</v>
       </c>
+      <c r="K138" t="n">
+        <v>185202.281719131</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.369325903358643</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B139" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C139" t="n">
         <v>462978</v>
@@ -7375,13 +8117,19 @@
       <c r="J139" t="n">
         <v>504</v>
       </c>
+      <c r="K139" t="n">
+        <v>238449.082338163</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.211365879481658</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B140" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C140" t="n">
         <v>1189557</v>
@@ -7407,13 +8155,19 @@
       <c r="J140" t="n">
         <v>1716</v>
       </c>
+      <c r="K140" t="n">
+        <v>247531.450104892</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.693245241876473</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B141" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C141" t="n">
         <v>103207</v>
@@ -7439,13 +8193,15 @@
       <c r="J141" t="n">
         <v>336</v>
       </c>
+      <c r="K141"/>
+      <c r="L141"/>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B142" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C142" t="n">
         <v>360881</v>
@@ -7471,13 +8227,19 @@
       <c r="J142" t="n">
         <v>1224</v>
       </c>
+      <c r="K142" t="n">
+        <v>186375.639894811</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.656738187829064</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C143" t="n">
         <v>221745</v>
@@ -7503,13 +8265,19 @@
       <c r="J143" t="n">
         <v>1428</v>
       </c>
+      <c r="K143" t="n">
+        <v>273688.241463779</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.521761546043251</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B144" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C144" t="n">
         <v>107914</v>
@@ -7535,13 +8303,19 @@
       <c r="J144" t="n">
         <v>1464</v>
       </c>
+      <c r="K144" t="n">
+        <v>232152.866278434</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.630618963904647</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B145" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C145" t="n">
         <v>125127</v>
@@ -7567,13 +8341,15 @@
       <c r="J145" t="n">
         <v>996</v>
       </c>
+      <c r="K145"/>
+      <c r="L145"/>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B146" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C146" t="n">
         <v>120338</v>
@@ -7599,13 +8375,19 @@
       <c r="J146" t="n">
         <v>480</v>
       </c>
+      <c r="K146" t="n">
+        <v>184252.181489336</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.260512519374313</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B147" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C147" t="n">
         <v>69126</v>
@@ -7625,13 +8407,15 @@
       <c r="J147" t="n">
         <v>1188</v>
       </c>
+      <c r="K147"/>
+      <c r="L147"/>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B148" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C148" t="n">
         <v>104184</v>
@@ -7657,13 +8441,19 @@
       <c r="J148" t="n">
         <v>2232</v>
       </c>
+      <c r="K148" t="n">
+        <v>135705.985512785</v>
+      </c>
+      <c r="L148" t="n">
+        <v>1.64473216974628</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C149" t="n">
         <v>77278</v>
@@ -7689,13 +8479,19 @@
       <c r="J149" t="n">
         <v>1008</v>
       </c>
+      <c r="K149" t="n">
+        <v>247662.309846668</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.407005813934332</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C150" t="n">
         <v>161260</v>
@@ -7721,13 +8517,19 @@
       <c r="J150" t="n">
         <v>528</v>
       </c>
+      <c r="K150" t="n">
+        <v>247481.278725379</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.213349471410281</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C151" t="n">
         <v>1178826</v>
@@ -7753,13 +8555,19 @@
       <c r="J151" t="n">
         <v>2124</v>
       </c>
+      <c r="K151" t="n">
+        <v>321263.687894367</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0.661139145205349</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B152" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C152" t="n">
         <v>88276</v>
@@ -7785,13 +8593,15 @@
       <c r="J152" t="n">
         <v>1296</v>
       </c>
+      <c r="K152"/>
+      <c r="L152"/>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B153" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C153" t="n">
         <v>369745</v>
@@ -7817,13 +8627,19 @@
       <c r="J153" t="n">
         <v>924</v>
       </c>
+      <c r="K153" t="n">
+        <v>344359.195127228</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.268324474291623</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B154" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C154" t="n">
         <v>334697</v>
@@ -7849,13 +8665,19 @@
       <c r="J154" t="n">
         <v>2208</v>
       </c>
+      <c r="K154" t="n">
+        <v>285006.160672073</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0.77472009545103</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C155" t="n">
         <v>73398</v>
@@ -7875,13 +8697,19 @@
       <c r="J155" t="n">
         <v>1248</v>
       </c>
+      <c r="K155" t="n">
+        <v>265419.914811083</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0.470198327389369</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C156" t="n">
         <v>70871</v>
@@ -7907,13 +8735,15 @@
       <c r="J156" t="n">
         <v>3876</v>
       </c>
+      <c r="K156"/>
+      <c r="L156"/>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B157" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C157" t="n">
         <v>800722</v>
@@ -7939,13 +8769,19 @@
       <c r="J157" t="n">
         <v>912</v>
       </c>
+      <c r="K157" t="n">
+        <v>173896.00967074</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.524451367070934</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B158" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C158" t="n">
         <v>996680</v>
@@ -7971,13 +8807,19 @@
       <c r="J158" t="n">
         <v>840</v>
       </c>
+      <c r="K158" t="n">
+        <v>290585.994820766</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0.289071054686622</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B159" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C159" t="n">
         <v>96289</v>
@@ -7997,13 +8839,19 @@
       <c r="J159" t="n">
         <v>552</v>
       </c>
+      <c r="K159" t="n">
+        <v>160864.976811653</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0.343144922493791</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B160" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C160" t="n">
         <v>426793</v>
@@ -8029,13 +8877,19 @@
       <c r="J160" t="n">
         <v>540</v>
       </c>
+      <c r="K160" t="n">
+        <v>210070.654040844</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.257056371088847</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B161" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C161" t="n">
         <v>312992</v>
@@ -8061,13 +8915,19 @@
       <c r="J161" t="n">
         <v>552</v>
       </c>
+      <c r="K161" t="n">
+        <v>209339.166236739</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.263686920093944</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B162" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C162" t="n">
         <v>139823</v>
@@ -8087,13 +8947,19 @@
       <c r="J162" t="n">
         <v>540</v>
       </c>
+      <c r="K162" t="n">
+        <v>122662.830677167</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0.440231158060595</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B163" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C163" t="n">
         <v>615361</v>
@@ -8119,13 +8985,19 @@
       <c r="J163" t="n">
         <v>1128</v>
       </c>
+      <c r="K163" t="n">
+        <v>218508.400685659</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0.516227292159222</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B164" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C164" t="n">
         <v>138838</v>
@@ -8151,13 +9023,19 @@
       <c r="J164" t="n">
         <v>852</v>
       </c>
+      <c r="K164" t="n">
+        <v>221288.7683346</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0.385017281451779</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B165" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C165" t="n">
         <v>1169048</v>
@@ -8183,13 +9061,19 @@
       <c r="J165" t="n">
         <v>3876</v>
       </c>
+      <c r="K165" t="n">
+        <v>241327.787626154</v>
+      </c>
+      <c r="L165" t="n">
+        <v>1.60611425568795</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C166" t="n">
         <v>156411</v>
@@ -8215,13 +9099,15 @@
       <c r="J166" t="n">
         <v>840</v>
       </c>
+      <c r="K166"/>
+      <c r="L166"/>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B167" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C167" t="n">
         <v>80966</v>
@@ -8247,13 +9133,19 @@
       <c r="J167" t="n">
         <v>1848</v>
       </c>
+      <c r="K167" t="n">
+        <v>955685.821734261</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0.193368987796269</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B168" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C168" t="n">
         <v>96327</v>
@@ -8279,13 +9171,19 @@
       <c r="J168" t="n">
         <v>516</v>
       </c>
+      <c r="K168" t="n">
+        <v>359986.223321426</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0.143338818702312</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B169" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C169" t="n">
         <v>92333</v>
@@ -8303,13 +9201,15 @@
       <c r="J169" t="n">
         <v>732</v>
       </c>
+      <c r="K169"/>
+      <c r="L169"/>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B170" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C170" t="n">
         <v>108140</v>
@@ -8335,13 +9235,15 @@
       <c r="J170" t="n">
         <v>2160</v>
       </c>
+      <c r="K170"/>
+      <c r="L170"/>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B171" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C171" t="n">
         <v>373031</v>
@@ -8367,13 +9269,19 @@
       <c r="J171" t="n">
         <v>1452</v>
       </c>
+      <c r="K171" t="n">
+        <v>246430.737092035</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0.589212213189834</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C172" t="n">
         <v>209790</v>
@@ -8399,13 +9307,19 @@
       <c r="J172" t="n">
         <v>1620</v>
       </c>
+      <c r="K172" t="n">
+        <v>605811.575932157</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0.267409878642104</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B173" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C173" t="n">
         <v>237393</v>
@@ -8431,13 +9345,19 @@
       <c r="J173" t="n">
         <v>2640</v>
       </c>
+      <c r="K173" t="n">
+        <v>444737.423323244</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0.593608691679898</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B174" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C174" t="n">
         <v>75151</v>
@@ -8453,13 +9373,15 @@
       <c r="J174" t="n">
         <v>696</v>
       </c>
+      <c r="K174"/>
+      <c r="L174"/>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B175" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C175" t="n">
         <v>122429</v>
@@ -8485,13 +9407,19 @@
       <c r="J175" t="n">
         <v>1548</v>
       </c>
+      <c r="K175" t="n">
+        <v>313929.169510788</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.493104862607169</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B176" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C176" t="n">
         <v>99902</v>
@@ -8517,13 +9445,19 @@
       <c r="J176" t="n">
         <v>1488</v>
       </c>
+      <c r="K176" t="n">
+        <v>265562.865717853</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0.560319303671366</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B177" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C177" t="n">
         <v>199206</v>
@@ -8549,13 +9483,15 @@
       <c r="J177" t="n">
         <v>540</v>
       </c>
+      <c r="K177"/>
+      <c r="L177"/>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B178" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C178" t="n">
         <v>7796182</v>
@@ -8581,13 +9517,19 @@
       <c r="J178" t="n">
         <v>1260</v>
       </c>
+      <c r="K178" t="n">
+        <v>161570.77074965</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0.779844023862669</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B179" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C179" t="n">
         <v>366760</v>
@@ -8613,13 +9555,19 @@
       <c r="J179" t="n">
         <v>552</v>
       </c>
+      <c r="K179" t="n">
+        <v>188625.610245128</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0.292643188421047</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B180" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C180" t="n">
         <v>542297</v>
@@ -8645,13 +9593,19 @@
       <c r="J180" t="n">
         <v>588</v>
       </c>
+      <c r="K180" t="n">
+        <v>184868.550177242</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0.318063834782205</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B181" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C181" t="n">
         <v>83722</v>
@@ -8671,13 +9625,15 @@
       <c r="J181" t="n">
         <v>1848</v>
       </c>
+      <c r="K181"/>
+      <c r="L181"/>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C182" t="n">
         <v>171773</v>
@@ -8703,13 +9659,19 @@
       <c r="J182" t="n">
         <v>456</v>
       </c>
+      <c r="K182" t="n">
+        <v>249481.978853584</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0.182778732995227</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B183" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C183" t="n">
         <v>82953</v>
@@ -8735,13 +9697,19 @@
       <c r="J183" t="n">
         <v>2724</v>
       </c>
+      <c r="K183" t="n">
+        <v>219584.459389108</v>
+      </c>
+      <c r="L183" t="n">
+        <v>1.24052494770271</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B184" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C184" t="n">
         <v>2173288</v>
@@ -8767,13 +9735,19 @@
       <c r="J184" t="n">
         <v>792</v>
       </c>
+      <c r="K184" t="n">
+        <v>220195.603584477</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0.359680205738601</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C185" t="n">
         <v>182711</v>
@@ -8799,13 +9773,19 @@
       <c r="J185" t="n">
         <v>1416</v>
       </c>
+      <c r="K185" t="n">
+        <v>184166.734123111</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0.768868496659902</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B186" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C186" t="n">
         <v>160233</v>
@@ -8831,13 +9811,19 @@
       <c r="J186" t="n">
         <v>636</v>
       </c>
+      <c r="K186" t="n">
+        <v>256381.785055364</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0.248067544994532</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C187" t="n">
         <v>605803</v>
@@ -8863,13 +9849,19 @@
       <c r="J187" t="n">
         <v>684</v>
       </c>
+      <c r="K187" t="n">
+        <v>189335.686015241</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0.361263116528883</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B188" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C188" t="n">
         <v>1760548</v>
@@ -8895,13 +9887,19 @@
       <c r="J188" t="n">
         <v>1212</v>
       </c>
+      <c r="K188" t="n">
+        <v>269704.029594418</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0.449381494901137</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B189" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C189" t="n">
         <v>212954</v>
@@ -8927,13 +9925,19 @@
       <c r="J189" t="n">
         <v>648</v>
       </c>
+      <c r="K189" t="n">
+        <v>302725.06492196</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0.214055615172483</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C190" t="n">
         <v>165461</v>
@@ -8959,13 +9963,19 @@
       <c r="J190" t="n">
         <v>2088</v>
       </c>
+      <c r="K190" t="n">
+        <v>233100.216508142</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0.895752063759695</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B191" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C191" t="n">
         <v>93825</v>
@@ -8985,13 +9995,15 @@
       <c r="J191" t="n">
         <v>876</v>
       </c>
+      <c r="K191"/>
+      <c r="L191"/>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B192" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C192" t="n">
         <v>215679</v>
@@ -9017,13 +10029,19 @@
       <c r="J192" t="n">
         <v>1932</v>
       </c>
+      <c r="K192" t="n">
+        <v>228648.607778749</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0.844964690040666</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B193" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C193" t="n">
         <v>130108</v>
@@ -9049,13 +10067,15 @@
       <c r="J193" t="n">
         <v>1752</v>
       </c>
+      <c r="K193"/>
+      <c r="L193"/>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B194" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C194" t="n">
         <v>163769</v>
@@ -9081,13 +10101,19 @@
       <c r="J194" t="n">
         <v>2832</v>
       </c>
+      <c r="K194" t="n">
+        <v>881648.144329628</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0.321216578088909</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C195" t="n">
         <v>264780</v>
@@ -9113,13 +10139,19 @@
       <c r="J195" t="n">
         <v>2712</v>
       </c>
+      <c r="K195" t="n">
+        <v>273988.044425515</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0.989824211376226</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B196" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C196" t="n">
         <v>114527</v>
@@ -9145,13 +10177,19 @@
       <c r="J196" t="n">
         <v>552</v>
       </c>
+      <c r="K196" t="n">
+        <v>568137.006693919</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0.0971596628095355</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C197" t="n">
         <v>106410</v>
@@ -9177,13 +10215,19 @@
       <c r="J197" t="n">
         <v>1488</v>
       </c>
+      <c r="K197" t="n">
+        <v>197876.168526276</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.751985451852131</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B198" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C198" t="n">
         <v>2254288</v>
@@ -9209,13 +10253,19 @@
       <c r="J198" t="n">
         <v>816</v>
       </c>
+      <c r="K198" t="n">
+        <v>209297.320086136</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0.38987599060713</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B199" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C199" t="n">
         <v>73840</v>
@@ -9241,13 +10291,19 @@
       <c r="J199" t="n">
         <v>3192</v>
       </c>
+      <c r="K199" t="n">
+        <v>806090.970583146</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0.395985083134082</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C200" t="n">
         <v>78078</v>
@@ -9273,13 +10329,19 @@
       <c r="J200" t="n">
         <v>3864</v>
       </c>
+      <c r="K200" t="n">
+        <v>274459.675502189</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1.40785708972726</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B201" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C201" t="n">
         <v>319428</v>
@@ -9305,13 +10367,19 @@
       <c r="J201" t="n">
         <v>516</v>
       </c>
+      <c r="K201" t="n">
+        <v>315538.951350679</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0.163529731524821</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B202" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C202" t="n">
         <v>168754</v>
@@ -9337,13 +10405,15 @@
       <c r="J202" t="n">
         <v>1332</v>
       </c>
+      <c r="K202"/>
+      <c r="L202"/>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B203" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C203" t="n">
         <v>80908</v>
@@ -9369,13 +10439,19 @@
       <c r="J203" t="n">
         <v>7044</v>
       </c>
+      <c r="K203" t="n">
+        <v>746087.199341306</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0.944125566853164</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B204" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C204" t="n">
         <v>509487</v>
@@ -9401,13 +10477,19 @@
       <c r="J204" t="n">
         <v>468</v>
       </c>
+      <c r="K204" t="n">
+        <v>155617.392594168</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0.30073759250066</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B205" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C205" t="n">
         <v>314259</v>
@@ -9433,13 +10515,19 @@
       <c r="J205" t="n">
         <v>1212</v>
       </c>
+      <c r="K205" t="n">
+        <v>205677.6760154</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.589271535676653</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B206" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C206" t="n">
         <v>182977</v>
@@ -9465,13 +10553,19 @@
       <c r="J206" t="n">
         <v>3408</v>
       </c>
+      <c r="K206" t="n">
+        <v>266238.256528182</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1.28005645936885</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B207" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C207" t="n">
         <v>711730</v>
@@ -9497,13 +10591,15 @@
       <c r="J207" t="n">
         <v>4092</v>
       </c>
+      <c r="K207"/>
+      <c r="L207"/>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C208" t="n">
         <v>957376</v>
@@ -9529,13 +10625,19 @@
       <c r="J208" t="n">
         <v>780</v>
       </c>
+      <c r="K208" t="n">
+        <v>318136.317413194</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0.245177918177427</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C209" t="n">
         <v>84082</v>
@@ -9561,13 +10663,19 @@
       <c r="J209" t="n">
         <v>792</v>
       </c>
+      <c r="K209" t="n">
+        <v>197460.760046587</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.401092348582646</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B210" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C210" t="n">
         <v>65257</v>
@@ -9593,13 +10701,19 @@
       <c r="J210" t="n">
         <v>960</v>
       </c>
+      <c r="K210" t="n">
+        <v>402581.380858474</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0.238461102685095</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B211" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C211" t="n">
         <v>170763</v>
@@ -9625,13 +10739,19 @@
       <c r="J211" t="n">
         <v>2688</v>
       </c>
+      <c r="K211" t="n">
+        <v>288566.14404747</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.931502206841638</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C212" t="n">
         <v>419704</v>
@@ -9657,13 +10777,19 @@
       <c r="J212" t="n">
         <v>720</v>
       </c>
+      <c r="K212" t="n">
+        <v>120257.634808602</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.598714585685914</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C213" t="n">
         <v>231353</v>
@@ -9689,13 +10815,19 @@
       <c r="J213" t="n">
         <v>372</v>
       </c>
+      <c r="K213" t="n">
+        <v>227139.335863716</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.163776123842856</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B214" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C214" t="n">
         <v>243719</v>
@@ -9721,13 +10853,15 @@
       <c r="J214" t="n">
         <v>588</v>
       </c>
+      <c r="K214"/>
+      <c r="L214"/>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B215" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C215" t="n">
         <v>226479</v>
@@ -9753,13 +10887,19 @@
       <c r="J215" t="n">
         <v>912</v>
       </c>
+      <c r="K215" t="n">
+        <v>238865.238701413</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.381805240878946</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B216" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C216" t="n">
         <v>852878</v>
@@ -9785,13 +10925,19 @@
       <c r="J216" t="n">
         <v>996</v>
       </c>
+      <c r="K216" t="n">
+        <v>167867.613225762</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0.593324692512603</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C217" t="n">
         <v>563293</v>
@@ -9817,13 +10963,19 @@
       <c r="J217" t="n">
         <v>1272</v>
       </c>
+      <c r="K217" t="n">
+        <v>286648.868787896</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0.443748480633709</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B218" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C218" t="n">
         <v>479971</v>
@@ -9849,13 +11001,19 @@
       <c r="J218" t="n">
         <v>972</v>
       </c>
+      <c r="K218" t="n">
+        <v>227453.808707017</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.427339513690902</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B219" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C219" t="n">
         <v>229366</v>
@@ -9881,13 +11039,19 @@
       <c r="J219" t="n">
         <v>588</v>
       </c>
+      <c r="K219" t="n">
+        <v>199706.218215224</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0.294432494518678</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C220" t="n">
         <v>2398871</v>
@@ -9913,13 +11077,19 @@
       <c r="J220" t="n">
         <v>1188</v>
       </c>
+      <c r="K220" t="n">
+        <v>251265.161084761</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0.472807290462064</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B221" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C221" t="n">
         <v>121989</v>
@@ -9945,13 +11115,19 @@
       <c r="J221" t="n">
         <v>1356</v>
       </c>
+      <c r="K221" t="n">
+        <v>165036.935811656</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.821634256193111</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C222" t="n">
         <v>126503</v>
@@ -9977,13 +11153,15 @@
       <c r="J222" t="n">
         <v>612</v>
       </c>
+      <c r="K222"/>
+      <c r="L222"/>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B223" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C223" t="n">
         <v>145319</v>
@@ -10009,13 +11187,19 @@
       <c r="J223" t="n">
         <v>972</v>
       </c>
+      <c r="K223" t="n">
+        <v>254888.708169525</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0.381342903332354</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B224" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C224" t="n">
         <v>224804</v>
@@ -10041,13 +11225,15 @@
       <c r="J224" t="n">
         <v>4284</v>
       </c>
+      <c r="K224"/>
+      <c r="L224"/>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B225" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C225" t="n">
         <v>65370</v>
@@ -10073,13 +11259,19 @@
       <c r="J225" t="n">
         <v>288</v>
       </c>
+      <c r="K225" t="n">
+        <v>307943.41445887</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0.093523675609717</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B226" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C226" t="n">
         <v>533366</v>
@@ -10105,13 +11297,19 @@
       <c r="J226" t="n">
         <v>588</v>
       </c>
+      <c r="K226" t="n">
+        <v>229415.073576104</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0.256303995563283</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B227" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C227" t="n">
         <v>211382</v>
@@ -10137,13 +11335,15 @@
       <c r="J227" t="n">
         <v>564</v>
       </c>
+      <c r="K227"/>
+      <c r="L227"/>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B228" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C228" t="n">
         <v>100866</v>
@@ -10169,13 +11369,19 @@
       <c r="J228" t="n">
         <v>984</v>
       </c>
+      <c r="K228" t="n">
+        <v>141220.981474991</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0.696780315306232</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B229" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C229" t="n">
         <v>351919</v>
@@ -10201,13 +11407,19 @@
       <c r="J229" t="n">
         <v>540</v>
       </c>
+      <c r="K229" t="n">
+        <v>209400.327734366</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0.257879252550653</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B230" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C230" t="n">
         <v>770959</v>
@@ -10233,13 +11445,19 @@
       <c r="J230" t="n">
         <v>516</v>
       </c>
+      <c r="K230" t="n">
+        <v>166656.269554727</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0.309619314880053</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B231" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C231" t="n">
         <v>160053</v>
@@ -10265,13 +11483,19 @@
       <c r="J231" t="n">
         <v>1368</v>
       </c>
+      <c r="K231" t="n">
+        <v>285522.834359257</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0.479121049309396</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B232" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C232" t="n">
         <v>295490</v>
@@ -10297,13 +11521,15 @@
       <c r="J232" t="n">
         <v>852</v>
       </c>
+      <c r="K232"/>
+      <c r="L232"/>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B233" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C233" t="n">
         <v>12927614</v>
@@ -10329,13 +11555,19 @@
       <c r="J233" t="n">
         <v>4116</v>
       </c>
+      <c r="K233" t="n">
+        <v>689167.736827839</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0.597242119740759</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B234" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C234" t="n">
         <v>1396762</v>
@@ -10361,13 +11593,19 @@
       <c r="J234" t="n">
         <v>852</v>
       </c>
+      <c r="K234" t="n">
+        <v>202814.907822374</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0.420087462577546</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B235" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C235" t="n">
         <v>367530</v>
@@ -10393,13 +11631,19 @@
       <c r="J235" t="n">
         <v>504</v>
       </c>
+      <c r="K235" t="n">
+        <v>145040.356506435</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0.34748949336569</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B236" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C236" t="n">
         <v>88094</v>
@@ -10425,13 +11669,15 @@
       <c r="J236" t="n">
         <v>324</v>
       </c>
+      <c r="K236"/>
+      <c r="L236"/>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B237" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C237" t="n">
         <v>267427</v>
@@ -10457,13 +11703,19 @@
       <c r="J237" t="n">
         <v>1164</v>
       </c>
+      <c r="K237" t="n">
+        <v>238324.594698811</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0.488409516219271</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B238" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C238" t="n">
         <v>236551</v>
@@ -10489,13 +11741,19 @@
       <c r="J238" t="n">
         <v>852</v>
       </c>
+      <c r="K238" t="n">
+        <v>189279.008166217</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0.45012915497307</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B239" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C239" t="n">
         <v>707606</v>
@@ -10521,13 +11779,19 @@
       <c r="J239" t="n">
         <v>1956</v>
       </c>
+      <c r="K239" t="n">
+        <v>307712.816771236</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0.635657630554321</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B240" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C240" t="n">
         <v>430462</v>
@@ -10553,13 +11817,19 @@
       <c r="J240" t="n">
         <v>3996</v>
       </c>
+      <c r="K240" t="n">
+        <v>361505.76561799</v>
+      </c>
+      <c r="L240" t="n">
+        <v>1.10537656105398</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C241" t="n">
         <v>134892</v>
@@ -10585,13 +11855,19 @@
       <c r="J241" t="n">
         <v>552</v>
       </c>
+      <c r="K241" t="n">
+        <v>198659.913631883</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0.277861794011879</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C242" t="n">
         <v>81513</v>
@@ -10615,13 +11891,19 @@
       <c r="J242" t="n">
         <v>1572</v>
       </c>
+      <c r="K242" t="n">
+        <v>218958.092301117</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0.717945604786392</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B243" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C243" t="n">
         <v>105193</v>
@@ -10647,13 +11929,19 @@
       <c r="J243" t="n">
         <v>2544</v>
       </c>
+      <c r="K243" t="n">
+        <v>229877.212451929</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1.10667776630187</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B244" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C244" t="n">
         <v>124853</v>
@@ -10679,13 +11967,19 @@
       <c r="J244" t="n">
         <v>2376</v>
       </c>
+      <c r="K244" t="n">
+        <v>200236.170193939</v>
+      </c>
+      <c r="L244" t="n">
+        <v>1.18659880365207</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B245" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C245" t="n">
         <v>66458</v>
@@ -10711,13 +12005,19 @@
       <c r="J245" t="n">
         <v>2760</v>
       </c>
+      <c r="K245" t="n">
+        <v>180535.743575142</v>
+      </c>
+      <c r="L245" t="n">
+        <v>1.52878313476535</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B246" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C246" t="n">
         <v>67064</v>
@@ -10735,13 +12035,15 @@
       <c r="J246" t="n">
         <v>288</v>
       </c>
+      <c r="K246"/>
+      <c r="L246"/>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B247" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C247" t="n">
         <v>67979</v>
@@ -10767,13 +12069,15 @@
       <c r="J247" t="n">
         <v>1140</v>
       </c>
+      <c r="K247"/>
+      <c r="L247"/>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B248" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C248" t="n">
         <v>914820</v>
@@ -10799,13 +12103,19 @@
       <c r="J248" t="n">
         <v>852</v>
       </c>
+      <c r="K248" t="n">
+        <v>151833.823820283</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0.561139789911674</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B249" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C249" t="n">
         <v>82089</v>
@@ -10831,13 +12141,19 @@
       <c r="J249" t="n">
         <v>2448</v>
       </c>
+      <c r="K249" t="n">
+        <v>201202.556628439</v>
+      </c>
+      <c r="L249" t="n">
+        <v>1.21668434090563</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B250" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C250" t="n">
         <v>221331</v>
@@ -10863,13 +12179,19 @@
       <c r="J250" t="n">
         <v>792</v>
       </c>
+      <c r="K250" t="n">
+        <v>247399.283270847</v>
+      </c>
+      <c r="L250" t="n">
+        <v>0.320130272622066</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B251" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C251" t="n">
         <v>1337653</v>
@@ -10895,13 +12217,19 @@
       <c r="J251" t="n">
         <v>816</v>
       </c>
+      <c r="K251" t="n">
+        <v>246965.088317785</v>
+      </c>
+      <c r="L251" t="n">
+        <v>0.330411073710145</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B252" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C252" t="n">
         <v>296774</v>
@@ -10925,13 +12253,19 @@
       <c r="J252" t="n">
         <v>1464</v>
       </c>
+      <c r="K252" t="n">
+        <v>273871.931570271</v>
+      </c>
+      <c r="L252" t="n">
+        <v>0.534556422633753</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B253" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C253" t="n">
         <v>6457988</v>
@@ -10957,13 +12291,19 @@
       <c r="J253" t="n">
         <v>4920</v>
       </c>
+      <c r="K253" t="n">
+        <v>301927.232258553</v>
+      </c>
+      <c r="L253" t="n">
+        <v>1.62953171305422</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B254" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C254" t="n">
         <v>111348</v>
@@ -10989,13 +12329,19 @@
       <c r="J254" t="n">
         <v>1188</v>
       </c>
+      <c r="K254" t="n">
+        <v>291936.083809453</v>
+      </c>
+      <c r="L254" t="n">
+        <v>0.40693839024552</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C255" t="n">
         <v>84022</v>
@@ -11021,13 +12367,19 @@
       <c r="J255" t="n">
         <v>3756</v>
       </c>
+      <c r="K255" t="n">
+        <v>259855.206319425</v>
+      </c>
+      <c r="L255" t="n">
+        <v>1.44542033742552</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C256" t="n">
         <v>188071</v>
@@ -11053,13 +12405,15 @@
       <c r="J256" t="n">
         <v>600</v>
       </c>
+      <c r="K256"/>
+      <c r="L256"/>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B257" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C257" t="n">
         <v>1574452</v>
@@ -11085,13 +12439,19 @@
       <c r="J257" t="n">
         <v>2700</v>
       </c>
+      <c r="K257" t="n">
+        <v>276286.099081431</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0.977247863347703</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B258" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C258" t="n">
         <v>3757952</v>
@@ -11117,13 +12477,19 @@
       <c r="J258" t="n">
         <v>3312</v>
       </c>
+      <c r="K258" t="n">
+        <v>217878.467907107</v>
+      </c>
+      <c r="L258" t="n">
+        <v>1.52011349804979</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C259" t="n">
         <v>75815</v>
@@ -11149,13 +12515,19 @@
       <c r="J259" t="n">
         <v>2712</v>
       </c>
+      <c r="K259" t="n">
+        <v>182786.079025654</v>
+      </c>
+      <c r="L259" t="n">
+        <v>1.48370161144458</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B260" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C260" t="n">
         <v>126608</v>
@@ -11181,13 +12553,19 @@
       <c r="J260" t="n">
         <v>588</v>
       </c>
+      <c r="K260" t="n">
+        <v>355416.659865121</v>
+      </c>
+      <c r="L260" t="n">
+        <v>0.165439628019447</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B261" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C261" t="n">
         <v>412339</v>
@@ -11213,13 +12591,19 @@
       <c r="J261" t="n">
         <v>468</v>
       </c>
+      <c r="K261" t="n">
+        <v>165821.971753797</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0.282230391455518</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B262" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C262" t="n">
         <v>556972</v>
@@ -11245,13 +12629,19 @@
       <c r="J262" t="n">
         <v>2112</v>
       </c>
+      <c r="K262" t="n">
+        <v>292144.35117457</v>
+      </c>
+      <c r="L262" t="n">
+        <v>0.722930288232059</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B263" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C263" t="n">
         <v>222072</v>
@@ -11277,13 +12667,19 @@
       <c r="J263" t="n">
         <v>2628</v>
       </c>
+      <c r="K263" t="n">
+        <v>118577.077882203</v>
+      </c>
+      <c r="L263" t="n">
+        <v>2.21627994797672</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B264" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C264" t="n">
         <v>156045</v>
@@ -11309,13 +12705,19 @@
       <c r="J264" t="n">
         <v>564</v>
       </c>
+      <c r="K264" t="n">
+        <v>258075.411092046</v>
+      </c>
+      <c r="L264" t="n">
+        <v>0.218540773649622</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B265" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C265" t="n">
         <v>386587</v>
@@ -11341,13 +12743,19 @@
       <c r="J265" t="n">
         <v>732</v>
       </c>
+      <c r="K265" t="n">
+        <v>187527.747055789</v>
+      </c>
+      <c r="L265" t="n">
+        <v>0.390342235478482</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C266" t="n">
         <v>80450</v>
@@ -11373,13 +12781,15 @@
       <c r="J266" t="n">
         <v>1620</v>
       </c>
+      <c r="K266"/>
+      <c r="L266"/>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B267" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C267" t="n">
         <v>70259</v>
@@ -11405,13 +12815,19 @@
       <c r="J267" t="n">
         <v>792</v>
       </c>
+      <c r="K267" t="n">
+        <v>482902.736792624</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0.164008182115587</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B268" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C268" t="n">
         <v>142752</v>
@@ -11437,13 +12853,19 @@
       <c r="J268" t="n">
         <v>804</v>
       </c>
+      <c r="K268" t="n">
+        <v>188331.438073134</v>
+      </c>
+      <c r="L268" t="n">
+        <v>0.42690695097214</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B269" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C269" t="n">
         <v>126932</v>
@@ -11469,13 +12891,19 @@
       <c r="J269" t="n">
         <v>324</v>
       </c>
+      <c r="K269" t="n">
+        <v>346432.403429975</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0.0935247386769034</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B270" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C270" t="n">
         <v>104717</v>
@@ -11501,13 +12929,19 @@
       <c r="J270" t="n">
         <v>288</v>
       </c>
+      <c r="K270" t="n">
+        <v>259059.297931665</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0.111171458542271</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B271" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C271" t="n">
         <v>71547</v>
@@ -11527,13 +12961,19 @@
       <c r="J271" t="n">
         <v>1704</v>
       </c>
+      <c r="K271" t="n">
+        <v>244402.988791531</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0.697209149702119</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B272" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C272" t="n">
         <v>65072</v>
@@ -11559,13 +12999,19 @@
       <c r="J272" t="n">
         <v>540</v>
       </c>
+      <c r="K272" t="n">
+        <v>209996.536293098</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0.257147098486571</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B273" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C273" t="n">
         <v>132736</v>
@@ -11591,13 +13037,19 @@
       <c r="J273" t="n">
         <v>552</v>
       </c>
+      <c r="K273" t="n">
+        <v>418805.496927816</v>
+      </c>
+      <c r="L273" t="n">
+        <v>0.131803427617174</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B274" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C274" t="n">
         <v>66035</v>
@@ -11623,13 +13075,15 @@
       <c r="J274" t="n">
         <v>1956</v>
       </c>
+      <c r="K274"/>
+      <c r="L274"/>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C275" t="n">
         <v>177428</v>
@@ -11655,13 +13109,19 @@
       <c r="J275" t="n">
         <v>852</v>
       </c>
+      <c r="K275" t="n">
+        <v>292921.546749109</v>
+      </c>
+      <c r="L275" t="n">
+        <v>0.290862863949625</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B276" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C276" t="n">
         <v>413391</v>
@@ -11687,13 +13147,19 @@
       <c r="J276" t="n">
         <v>1296</v>
       </c>
+      <c r="K276" t="n">
+        <v>255469.341120072</v>
+      </c>
+      <c r="L276" t="n">
+        <v>0.507301578466464</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C277" t="n">
         <v>65728</v>
@@ -11719,13 +13185,15 @@
       <c r="J277" t="n">
         <v>288</v>
       </c>
+      <c r="K277"/>
+      <c r="L277"/>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B278" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C278" t="n">
         <v>132727</v>
@@ -11751,13 +13219,19 @@
       <c r="J278" t="n">
         <v>3228</v>
       </c>
+      <c r="K278" t="n">
+        <v>651353.16219355</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0.495583684453013</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B279" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C279" t="n">
         <v>416233</v>
@@ -11783,13 +13257,19 @@
       <c r="J279" t="n">
         <v>6348</v>
       </c>
+      <c r="K279" t="n">
+        <v>463324.394124001</v>
+      </c>
+      <c r="L279" t="n">
+        <v>1.37009837610689</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B280" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C280" t="n">
         <v>2151715</v>
@@ -11815,13 +13295,19 @@
       <c r="J280" t="n">
         <v>1056</v>
       </c>
+      <c r="K280" t="n">
+        <v>359057.029551131</v>
+      </c>
+      <c r="L280" t="n">
+        <v>0.294103697487873</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B281" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C281" t="n">
         <v>126773</v>
@@ -11847,13 +13333,19 @@
       <c r="J281" t="n">
         <v>1032</v>
       </c>
+      <c r="K281" t="n">
+        <v>241925.21571266</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0.426578104708906</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B282" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C282" t="n">
         <v>576718</v>
@@ -11879,13 +13371,19 @@
       <c r="J282" t="n">
         <v>4056</v>
       </c>
+      <c r="K282" t="n">
+        <v>250297.467893125</v>
+      </c>
+      <c r="L282" t="n">
+        <v>1.62047184661568</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B283" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C283" t="n">
         <v>966230</v>
@@ -11911,13 +13409,19 @@
       <c r="J283" t="n">
         <v>1176</v>
       </c>
+      <c r="K283" t="n">
+        <v>198650.717705293</v>
+      </c>
+      <c r="L283" t="n">
+        <v>0.591993833993918</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B284" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C284" t="n">
         <v>19940274</v>
@@ -11943,13 +13447,19 @@
       <c r="J284" t="n">
         <v>6696</v>
       </c>
+      <c r="K284" t="n">
+        <v>543045.897143517</v>
+      </c>
+      <c r="L284" t="n">
+        <v>1.2330449479909</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B285" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C285" t="n">
         <v>152703</v>
@@ -11975,13 +13485,19 @@
       <c r="J285" t="n">
         <v>1860</v>
       </c>
+      <c r="K285" t="n">
+        <v>330530.504888686</v>
+      </c>
+      <c r="L285" t="n">
+        <v>0.562731721426559</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B286" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C286" t="n">
         <v>934956</v>
@@ -12007,13 +13523,19 @@
       <c r="J286" t="n">
         <v>3300</v>
       </c>
+      <c r="K286" t="n">
+        <v>344261.386100058</v>
+      </c>
+      <c r="L286" t="n">
+        <v>0.958573959567126</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B287" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C287" t="n">
         <v>66186</v>
@@ -12033,13 +13555,19 @@
       <c r="J287" t="n">
         <v>1344</v>
       </c>
+      <c r="K287" t="n">
+        <v>189131.56503798</v>
+      </c>
+      <c r="L287" t="n">
+        <v>0.710616442966625</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B288" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C288" t="n">
         <v>282602</v>
@@ -12065,13 +13593,19 @@
       <c r="J288" t="n">
         <v>3012</v>
       </c>
+      <c r="K288" t="n">
+        <v>242682.070818221</v>
+      </c>
+      <c r="L288" t="n">
+        <v>1.24113000595586</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C289" t="n">
         <v>86478</v>
@@ -12097,13 +13631,19 @@
       <c r="J289" t="n">
         <v>1056</v>
       </c>
+      <c r="K289" t="n">
+        <v>349088.595794213</v>
+      </c>
+      <c r="L289" t="n">
+        <v>0.302502004569209</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B290" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C290" t="n">
         <v>428905</v>
@@ -12129,13 +13669,19 @@
       <c r="J290" t="n">
         <v>2064</v>
       </c>
+      <c r="K290" t="n">
+        <v>127804.967194624</v>
+      </c>
+      <c r="L290" t="n">
+        <v>1.61496070560145</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B291" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C291" t="n">
         <v>669210</v>
@@ -12161,13 +13707,19 @@
       <c r="J291" t="n">
         <v>1392</v>
       </c>
+      <c r="K291" t="n">
+        <v>370284.054398106</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0.375927611104584</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B292" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C292" t="n">
         <v>1497821</v>
@@ -12193,13 +13745,19 @@
       <c r="J292" t="n">
         <v>576</v>
       </c>
+      <c r="K292" t="n">
+        <v>124785.284656463</v>
+      </c>
+      <c r="L292" t="n">
+        <v>0.461592888605208</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B293" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C293" t="n">
         <v>75475</v>
@@ -12223,13 +13781,15 @@
       <c r="J293" t="n">
         <v>3792</v>
       </c>
+      <c r="K293"/>
+      <c r="L293"/>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B294" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C294" t="n">
         <v>302912</v>
@@ -12255,13 +13815,19 @@
       <c r="J294" t="n">
         <v>696</v>
       </c>
+      <c r="K294" t="n">
+        <v>346412.524847002</v>
+      </c>
+      <c r="L294" t="n">
+        <v>0.20091652295407</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B295" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C295" t="n">
         <v>1001186</v>
@@ -12287,13 +13853,19 @@
       <c r="J295" t="n">
         <v>588</v>
       </c>
+      <c r="K295" t="n">
+        <v>223108.192176519</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0.263549264714935</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B296" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C296" t="n">
         <v>80869</v>
@@ -12311,13 +13883,15 @@
       <c r="J296" t="n">
         <v>468</v>
       </c>
+      <c r="K296"/>
+      <c r="L296"/>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B297" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C297" t="n">
         <v>2940513</v>
@@ -12343,13 +13917,19 @@
       <c r="J297" t="n">
         <v>1500</v>
       </c>
+      <c r="K297" t="n">
+        <v>217061.899104191</v>
+      </c>
+      <c r="L297" t="n">
+        <v>0.691047118905005</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B298" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C298" t="n">
         <v>173307</v>
@@ -12375,13 +13955,19 @@
       <c r="J298" t="n">
         <v>2376</v>
       </c>
+      <c r="K298" t="n">
+        <v>247852.645402478</v>
+      </c>
+      <c r="L298" t="n">
+        <v>0.958634109449069</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B299" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C299" t="n">
         <v>145406</v>
@@ -12407,13 +13993,15 @@
       <c r="J299" t="n">
         <v>1164</v>
       </c>
+      <c r="K299"/>
+      <c r="L299"/>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B300" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C300" t="n">
         <v>72136</v>
@@ -12439,13 +14027,19 @@
       <c r="J300" t="n">
         <v>2016</v>
       </c>
+      <c r="K300" t="n">
+        <v>326072.358302747</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0.618267678528032</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B301" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C301" t="n">
         <v>835427</v>
@@ -12471,13 +14065,19 @@
       <c r="J301" t="n">
         <v>2904</v>
       </c>
+      <c r="K301" t="n">
+        <v>594495.07615253</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0.488481758132328</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B302" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C302" t="n">
         <v>99814</v>
@@ -12503,13 +14103,19 @@
       <c r="J302" t="n">
         <v>504</v>
       </c>
+      <c r="K302" t="n">
+        <v>259138.479193076</v>
+      </c>
+      <c r="L302" t="n">
+        <v>0.194490606554994</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B303" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C303" t="n">
         <v>658447</v>
@@ -12535,13 +14141,19 @@
       <c r="J303" t="n">
         <v>1524</v>
       </c>
+      <c r="K303" t="n">
+        <v>266438.121248141</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0.571990221542157</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C304" t="n">
         <v>226221</v>
@@ -12567,13 +14179,19 @@
       <c r="J304" t="n">
         <v>1572</v>
       </c>
+      <c r="K304" t="n">
+        <v>449144.873641649</v>
+      </c>
+      <c r="L304" t="n">
+        <v>0.349998428625999</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B305" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C305" t="n">
         <v>538928</v>
@@ -12599,13 +14217,19 @@
       <c r="J305" t="n">
         <v>552</v>
       </c>
+      <c r="K305" t="n">
+        <v>532115.15656292</v>
+      </c>
+      <c r="L305" t="n">
+        <v>0.103736943628053</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B306" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C306" t="n">
         <v>365668</v>
@@ -12631,13 +14255,19 @@
       <c r="J306" t="n">
         <v>768</v>
       </c>
+      <c r="K306" t="n">
+        <v>145141.211914839</v>
+      </c>
+      <c r="L306" t="n">
+        <v>0.529139856190964</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B307" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C307" t="n">
         <v>6330422</v>
@@ -12663,13 +14293,19 @@
       <c r="J307" t="n">
         <v>1956</v>
       </c>
+      <c r="K307" t="n">
+        <v>274263.96569573</v>
+      </c>
+      <c r="L307" t="n">
+        <v>0.713181549401934</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B308" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C308" t="n">
         <v>5186958</v>
@@ -12695,13 +14331,19 @@
       <c r="J308" t="n">
         <v>1272</v>
       </c>
+      <c r="K308" t="n">
+        <v>299348.435659138</v>
+      </c>
+      <c r="L308" t="n">
+        <v>0.42492288199174</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B309" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C309" t="n">
         <v>70482</v>
@@ -12721,13 +14363,15 @@
       <c r="J309" t="n">
         <v>444</v>
       </c>
+      <c r="K309"/>
+      <c r="L309"/>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B310" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C310" t="n">
         <v>108417</v>
@@ -12753,13 +14397,19 @@
       <c r="J310" t="n">
         <v>1632</v>
       </c>
+      <c r="K310" t="n">
+        <v>282093.95631591</v>
+      </c>
+      <c r="L310" t="n">
+        <v>0.578530650324308</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B311" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C311" t="n">
         <v>2429917</v>
@@ -12785,13 +14435,19 @@
       <c r="J311" t="n">
         <v>1392</v>
       </c>
+      <c r="K311" t="n">
+        <v>201744.538774426</v>
+      </c>
+      <c r="L311" t="n">
+        <v>0.689981502575602</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B312" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C312" t="n">
         <v>128726</v>
@@ -12817,13 +14473,19 @@
       <c r="J312" t="n">
         <v>5100</v>
       </c>
+      <c r="K312" t="n">
+        <v>382930.654755506</v>
+      </c>
+      <c r="L312" t="n">
+        <v>1.33183382857041</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B313" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C313" t="n">
         <v>77871</v>
@@ -12849,13 +14511,15 @@
       <c r="J313" t="n">
         <v>2868</v>
       </c>
+      <c r="K313"/>
+      <c r="L313"/>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B314" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C314" t="n">
         <v>91010</v>
@@ -12881,13 +14545,19 @@
       <c r="J314" t="n">
         <v>720</v>
       </c>
+      <c r="K314" t="n">
+        <v>236943.182558214</v>
+      </c>
+      <c r="L314" t="n">
+        <v>0.303870317021299</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B315" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C315" t="n">
         <v>77958</v>
@@ -12913,13 +14583,19 @@
       <c r="J315" t="n">
         <v>684</v>
       </c>
+      <c r="K315" t="n">
+        <v>390153.344456857</v>
+      </c>
+      <c r="L315" t="n">
+        <v>0.175315682850858</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B316" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C316" t="n">
         <v>571534</v>
@@ -12945,13 +14621,19 @@
       <c r="J316" t="n">
         <v>2796</v>
       </c>
+      <c r="K316" t="n">
+        <v>465942.220677653</v>
+      </c>
+      <c r="L316" t="n">
+        <v>0.600074403202521</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B317" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C317" t="n">
         <v>2537070</v>
@@ -12977,13 +14659,19 @@
       <c r="J317" t="n">
         <v>1116</v>
       </c>
+      <c r="K317" t="n">
+        <v>328636.509474776</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0.339584911543633</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B318" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C318" t="n">
         <v>556336</v>
@@ -13009,13 +14697,19 @@
       <c r="J318" t="n">
         <v>4152</v>
       </c>
+      <c r="K318" t="n">
+        <v>270299.370749965</v>
+      </c>
+      <c r="L318" t="n">
+        <v>1.53607460812061</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B319" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C319" t="n">
         <v>144523</v>
@@ -13041,13 +14735,15 @@
       <c r="J319" t="n">
         <v>1512</v>
       </c>
+      <c r="K319"/>
+      <c r="L319"/>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C320" t="n">
         <v>252013</v>
@@ -13073,13 +14769,15 @@
       <c r="J320" t="n">
         <v>780</v>
       </c>
+      <c r="K320"/>
+      <c r="L320"/>
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B321" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C321" t="n">
         <v>1700901</v>
@@ -13105,13 +14803,19 @@
       <c r="J321" t="n">
         <v>3852</v>
       </c>
+      <c r="K321" t="n">
+        <v>364872.268599493</v>
+      </c>
+      <c r="L321" t="n">
+        <v>1.05571191112586</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B322" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C322" t="n">
         <v>760154</v>
@@ -13137,13 +14841,19 @@
       <c r="J322" t="n">
         <v>1272</v>
       </c>
+      <c r="K322" t="n">
+        <v>329907.703748711</v>
+      </c>
+      <c r="L322" t="n">
+        <v>0.385562381704452</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B323" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C323" t="n">
         <v>169866</v>
@@ -13169,13 +14879,19 @@
       <c r="J323" t="n">
         <v>1488</v>
       </c>
+      <c r="K323" t="n">
+        <v>224874.138094466</v>
+      </c>
+      <c r="L323" t="n">
+        <v>0.661703481160166</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B324" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C324" t="n">
         <v>212122</v>
@@ -13201,13 +14917,19 @@
       <c r="J324" t="n">
         <v>2556</v>
       </c>
+      <c r="K324" t="n">
+        <v>260151.678448246</v>
+      </c>
+      <c r="L324" t="n">
+        <v>0.98250375136768</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B325" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C325" t="n">
         <v>97701</v>
@@ -13233,13 +14955,15 @@
       <c r="J325" t="n">
         <v>3132</v>
       </c>
+      <c r="K325"/>
+      <c r="L325"/>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B326" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C326" t="n">
         <v>198651</v>
@@ -13265,13 +14989,19 @@
       <c r="J326" t="n">
         <v>2256</v>
       </c>
+      <c r="K326" t="n">
+        <v>232499.054088086</v>
+      </c>
+      <c r="L326" t="n">
+        <v>0.970326528358813</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B327" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C327" t="n">
         <v>1562009</v>
@@ -13297,13 +15027,19 @@
       <c r="J327" t="n">
         <v>888</v>
       </c>
+      <c r="K327" t="n">
+        <v>320011.452325065</v>
+      </c>
+      <c r="L327" t="n">
+        <v>0.277490069042272</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B328" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C328" t="n">
         <v>153470</v>
@@ -13329,13 +15065,19 @@
       <c r="J328" t="n">
         <v>468</v>
       </c>
+      <c r="K328" t="n">
+        <v>314047.999242186</v>
+      </c>
+      <c r="L328" t="n">
+        <v>0.149021805943457</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C329" t="n">
         <v>439117</v>
@@ -13361,13 +15103,19 @@
       <c r="J329" t="n">
         <v>1764</v>
       </c>
+      <c r="K329" t="n">
+        <v>205742.998946954</v>
+      </c>
+      <c r="L329" t="n">
+        <v>0.857380328384737</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C330" t="n">
         <v>181121</v>
@@ -13393,13 +15141,19 @@
       <c r="J330" t="n">
         <v>1752</v>
       </c>
+      <c r="K330" t="n">
+        <v>248885.39502456</v>
+      </c>
+      <c r="L330" t="n">
+        <v>0.703938453209402</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B331" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C331" t="n">
         <v>575266</v>
@@ -13425,13 +15179,19 @@
       <c r="J331" t="n">
         <v>912</v>
       </c>
+      <c r="K331" t="n">
+        <v>325332.046454838</v>
+      </c>
+      <c r="L331" t="n">
+        <v>0.280328977713114</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B332" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C332" t="n">
         <v>72352</v>
@@ -13457,13 +15217,19 @@
       <c r="J332" t="n">
         <v>792</v>
       </c>
+      <c r="K332" t="n">
+        <v>190996.778424065</v>
+      </c>
+      <c r="L332" t="n">
+        <v>0.414666680001033</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B333" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C333" t="n">
         <v>66410</v>
@@ -13485,13 +15251,15 @@
       <c r="J333" t="n">
         <v>288</v>
       </c>
+      <c r="K333"/>
+      <c r="L333"/>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C334" t="n">
         <v>1368219</v>
@@ -13517,13 +15285,19 @@
       <c r="J334" t="n">
         <v>1272</v>
       </c>
+      <c r="K334" t="n">
+        <v>330227.345293132</v>
+      </c>
+      <c r="L334" t="n">
+        <v>0.385189178949092</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B335" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C335" t="n">
         <v>128517</v>
@@ -13549,13 +15323,19 @@
       <c r="J335" t="n">
         <v>288</v>
       </c>
+      <c r="K335" t="n">
+        <v>258129.078772039</v>
+      </c>
+      <c r="L335" t="n">
+        <v>0.111572086868346</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C336" t="n">
         <v>79468</v>
@@ -13581,13 +15361,15 @@
       <c r="J336" t="n">
         <v>2724</v>
       </c>
+      <c r="K336"/>
+      <c r="L336"/>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B337" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C337" t="n">
         <v>4744214</v>
@@ -13613,13 +15395,19 @@
       <c r="J337" t="n">
         <v>2100</v>
       </c>
+      <c r="K337" t="n">
+        <v>490712.265514889</v>
+      </c>
+      <c r="L337" t="n">
+        <v>0.427949360058594</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B338" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C338" t="n">
         <v>315456</v>
@@ -13645,13 +15433,19 @@
       <c r="J338" t="n">
         <v>1284</v>
       </c>
+      <c r="K338" t="n">
+        <v>241392.508361553</v>
+      </c>
+      <c r="L338" t="n">
+        <v>0.531913773428648</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B339" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C339" t="n">
         <v>230742</v>
@@ -13677,13 +15471,19 @@
       <c r="J339" t="n">
         <v>2532</v>
       </c>
+      <c r="K339" t="n">
+        <v>173284.50608851</v>
+      </c>
+      <c r="L339" t="n">
+        <v>1.46118083904554</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B340" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C340" t="n">
         <v>1057218</v>
@@ -13709,13 +15509,19 @@
       <c r="J340" t="n">
         <v>2952</v>
       </c>
+      <c r="K340" t="n">
+        <v>230696.738601169</v>
+      </c>
+      <c r="L340" t="n">
+        <v>1.27960196485632</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B341" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C341" t="n">
         <v>337103</v>
@@ -13741,13 +15547,19 @@
       <c r="J341" t="n">
         <v>1884</v>
       </c>
+      <c r="K341" t="n">
+        <v>173951.562536614</v>
+      </c>
+      <c r="L341" t="n">
+        <v>1.08306011887846</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B342" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C342" t="n">
         <v>147114</v>
@@ -13773,13 +15585,15 @@
       <c r="J342" t="n">
         <v>600</v>
       </c>
+      <c r="K342"/>
+      <c r="L342"/>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B343" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C343" t="n">
         <v>2463127</v>
@@ -13805,13 +15619,19 @@
       <c r="J343" t="n">
         <v>1896</v>
       </c>
+      <c r="K343" t="n">
+        <v>361812.117896984</v>
+      </c>
+      <c r="L343" t="n">
+        <v>0.524028883007129</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C344" t="n">
         <v>205878</v>
@@ -13837,13 +15657,19 @@
       <c r="J344" t="n">
         <v>1680</v>
       </c>
+      <c r="K344" t="n">
+        <v>143928.743571367</v>
+      </c>
+      <c r="L344" t="n">
+        <v>1.16724426150984</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B345" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C345" t="n">
         <v>207943</v>
@@ -13869,13 +15695,19 @@
       <c r="J345" t="n">
         <v>1344</v>
       </c>
+      <c r="K345" t="n">
+        <v>332489.53726887</v>
+      </c>
+      <c r="L345" t="n">
+        <v>0.404223245952298</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B346" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C346" t="n">
         <v>119186</v>
@@ -13901,13 +15733,15 @@
       <c r="J346" t="n">
         <v>480</v>
       </c>
+      <c r="K346"/>
+      <c r="L346"/>
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B347" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C347" t="n">
         <v>2809527</v>
@@ -13933,13 +15767,19 @@
       <c r="J347" t="n">
         <v>600</v>
       </c>
+      <c r="K347" t="n">
+        <v>201396.454557642</v>
+      </c>
+      <c r="L347" t="n">
+        <v>0.297919842391403</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B348" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C348" t="n">
         <v>99823</v>
@@ -13965,13 +15805,19 @@
       <c r="J348" t="n">
         <v>1920</v>
       </c>
+      <c r="K348" t="n">
+        <v>177641.821398853</v>
+      </c>
+      <c r="L348" t="n">
+        <v>1.080826567123</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B349" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C349" t="n">
         <v>443416</v>
@@ -13997,13 +15843,19 @@
       <c r="J349" t="n">
         <v>708</v>
       </c>
+      <c r="K349" t="n">
+        <v>289896.405253239</v>
+      </c>
+      <c r="L349" t="n">
+        <v>0.244225173948441</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B350" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C350" t="n">
         <v>436251</v>
@@ -14029,13 +15881,19 @@
       <c r="J350" t="n">
         <v>2856</v>
       </c>
+      <c r="K350" t="n">
+        <v>638717.38664094</v>
+      </c>
+      <c r="L350" t="n">
+        <v>0.447146118100825</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C351" t="n">
         <v>131570</v>
@@ -14061,13 +15919,19 @@
       <c r="J351" t="n">
         <v>600</v>
       </c>
+      <c r="K351" t="n">
+        <v>452912.345652472</v>
+      </c>
+      <c r="L351" t="n">
+        <v>0.132475964888003</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B352" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C352" t="n">
         <v>1300762</v>
@@ -14093,13 +15957,19 @@
       <c r="J352" t="n">
         <v>2280</v>
       </c>
+      <c r="K352" t="n">
+        <v>439573.011604988</v>
+      </c>
+      <c r="L352" t="n">
+        <v>0.518685164877426</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B353" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C353" t="n">
         <v>121408</v>
@@ -14125,13 +15995,15 @@
       <c r="J353" t="n">
         <v>288</v>
       </c>
+      <c r="K353"/>
+      <c r="L353"/>
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B354" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C354" t="n">
         <v>2763006</v>
@@ -14157,13 +16029,19 @@
       <c r="J354" t="n">
         <v>696</v>
       </c>
+      <c r="K354" t="n">
+        <v>197097.750642708</v>
+      </c>
+      <c r="L354" t="n">
+        <v>0.353124273478739</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B355" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C355" t="n">
         <v>3298799</v>
@@ -14189,13 +16067,19 @@
       <c r="J355" t="n">
         <v>3324</v>
       </c>
+      <c r="K355" t="n">
+        <v>662642.493283885</v>
+      </c>
+      <c r="L355" t="n">
+        <v>0.501627956807768</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B356" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C356" t="n">
         <v>113533</v>
@@ -14221,13 +16105,19 @@
       <c r="J356" t="n">
         <v>3048</v>
       </c>
+      <c r="K356" t="n">
+        <v>271423.940260913</v>
+      </c>
+      <c r="L356" t="n">
+        <v>1.12296652869678</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B357" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C357" t="n">
         <v>68537</v>
@@ -14247,13 +16137,15 @@
       <c r="J357" t="n">
         <v>744</v>
       </c>
+      <c r="K357"/>
+      <c r="L357"/>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B358" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C358" t="n">
         <v>4648486</v>
@@ -14279,13 +16171,19 @@
       <c r="J358" t="n">
         <v>4188</v>
       </c>
+      <c r="K358" t="n">
+        <v>759257.200719639</v>
+      </c>
+      <c r="L358" t="n">
+        <v>0.551591739404056</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B359" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C359" t="n">
         <v>1995484</v>
@@ -14311,13 +16209,19 @@
       <c r="J359" t="n">
         <v>4344</v>
       </c>
+      <c r="K359" t="n">
+        <v>868513.085407609</v>
+      </c>
+      <c r="L359" t="n">
+        <v>0.500165175745312</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B360" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C360" t="n">
         <v>281843</v>
@@ -14343,13 +16247,19 @@
       <c r="J360" t="n">
         <v>1788</v>
       </c>
+      <c r="K360" t="n">
+        <v>603510.896250969</v>
+      </c>
+      <c r="L360" t="n">
+        <v>0.296266399017337</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B361" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C361" t="n">
         <v>262406</v>
@@ -14375,13 +16285,19 @@
       <c r="J361" t="n">
         <v>3744</v>
       </c>
+      <c r="K361" t="n">
+        <v>749715.964005264</v>
+      </c>
+      <c r="L361" t="n">
+        <v>0.499389125982879</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B362" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C362" t="n">
         <v>157765</v>
@@ -14407,13 +16323,19 @@
       <c r="J362" t="n">
         <v>1164</v>
       </c>
+      <c r="K362" t="n">
+        <v>398901.630396199</v>
+      </c>
+      <c r="L362" t="n">
+        <v>0.291801264097087</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B363" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C363" t="n">
         <v>444500</v>
@@ -14439,13 +16361,19 @@
       <c r="J363" t="n">
         <v>2880</v>
       </c>
+      <c r="K363" t="n">
+        <v>809438.988522187</v>
+      </c>
+      <c r="L363" t="n">
+        <v>0.355801986417542</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B364" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C364" t="n">
         <v>485375</v>
@@ -14471,13 +16399,19 @@
       <c r="J364" t="n">
         <v>2448</v>
       </c>
+      <c r="K364" t="n">
+        <v>475430.50450821</v>
+      </c>
+      <c r="L364" t="n">
+        <v>0.514901752577327</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B365" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C365" t="n">
         <v>431589</v>
@@ -14503,13 +16437,19 @@
       <c r="J365" t="n">
         <v>984</v>
       </c>
+      <c r="K365" t="n">
+        <v>329812.086959566</v>
+      </c>
+      <c r="L365" t="n">
+        <v>0.298351709626893</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B366" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C366" t="n">
         <v>574009</v>
@@ -14535,13 +16475,19 @@
       <c r="J366" t="n">
         <v>1416</v>
       </c>
+      <c r="K366" t="n">
+        <v>251919.061304988</v>
+      </c>
+      <c r="L366" t="n">
+        <v>0.56208529543769</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B367" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C367" t="n">
         <v>271134</v>
@@ -14567,13 +16513,15 @@
       <c r="J367" t="n">
         <v>1920</v>
       </c>
+      <c r="K367"/>
+      <c r="L367"/>
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B368" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C368" t="n">
         <v>79091</v>
@@ -14599,13 +16547,15 @@
       <c r="J368" t="n">
         <v>288</v>
       </c>
+      <c r="K368"/>
+      <c r="L368"/>
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B369" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C369" t="n">
         <v>4145494</v>
@@ -14631,13 +16581,19 @@
       <c r="J369" t="n">
         <v>1236</v>
       </c>
+      <c r="K369" t="n">
+        <v>487939.926439314</v>
+      </c>
+      <c r="L369" t="n">
+        <v>0.25330987136461</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B370" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C370" t="n">
         <v>172139</v>
@@ -14663,13 +16619,19 @@
       <c r="J370" t="n">
         <v>3456</v>
       </c>
+      <c r="K370" t="n">
+        <v>264072.90709454</v>
+      </c>
+      <c r="L370" t="n">
+        <v>1.3087294861198</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B371" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C371" t="n">
         <v>109778</v>
@@ -14695,13 +16657,19 @@
       <c r="J371" t="n">
         <v>876</v>
       </c>
+      <c r="K371" t="n">
+        <v>151237.852795565</v>
+      </c>
+      <c r="L371" t="n">
+        <v>0.579220072096716</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B372" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C372" t="n">
         <v>82475</v>
@@ -14727,13 +16695,19 @@
       <c r="J372" t="n">
         <v>1404</v>
       </c>
+      <c r="K372" t="n">
+        <v>266243.909805208</v>
+      </c>
+      <c r="L372" t="n">
+        <v>0.527336005930506</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B373" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C373" t="n">
         <v>74446</v>
@@ -14753,13 +16727,15 @@
       <c r="J373" t="n">
         <v>804</v>
       </c>
+      <c r="K373"/>
+      <c r="L373"/>
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B374" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C374" t="n">
         <v>118331</v>
@@ -14785,13 +16761,19 @@
       <c r="J374" t="n">
         <v>2628</v>
       </c>
+      <c r="K374" t="n">
+        <v>267770.073360372</v>
+      </c>
+      <c r="L374" t="n">
+        <v>0.981439026034536</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B375" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C375" t="n">
         <v>69632</v>
@@ -14811,13 +16793,15 @@
       <c r="J375" t="n">
         <v>552</v>
       </c>
+      <c r="K375"/>
+      <c r="L375"/>
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B376" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C376" t="n">
         <v>150532</v>
@@ -14843,13 +16827,15 @@
       <c r="J376" t="n">
         <v>636</v>
       </c>
+      <c r="K376"/>
+      <c r="L376"/>
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B377" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C377" t="n">
         <v>383269</v>
@@ -14875,13 +16861,19 @@
       <c r="J377" t="n">
         <v>708</v>
       </c>
+      <c r="K377" t="n">
+        <v>95250.1066032741</v>
+      </c>
+      <c r="L377" t="n">
+        <v>0.743306254709917</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B378" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C378" t="n">
         <v>125773</v>
@@ -14907,13 +16899,19 @@
       <c r="J378" t="n">
         <v>1344</v>
       </c>
+      <c r="K378" t="n">
+        <v>163362.174906404</v>
+      </c>
+      <c r="L378" t="n">
+        <v>0.822711867523817</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B379" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C379" t="n">
         <v>308711</v>
@@ -14939,13 +16937,19 @@
       <c r="J379" t="n">
         <v>1824</v>
       </c>
+      <c r="K379" t="n">
+        <v>215511.384328079</v>
+      </c>
+      <c r="L379" t="n">
+        <v>0.846359001259662</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B380" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C380" t="n">
         <v>277615</v>
@@ -14971,13 +16975,15 @@
       <c r="J380" t="n">
         <v>768</v>
       </c>
+      <c r="K380"/>
+      <c r="L380"/>
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B381" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C381" t="n">
         <v>72134</v>
@@ -15003,13 +17009,19 @@
       <c r="J381" t="n">
         <v>3432</v>
       </c>
+      <c r="K381" t="n">
+        <v>285196.258998878</v>
+      </c>
+      <c r="L381" t="n">
+        <v>1.20338184380375</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B382" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C382" t="n">
         <v>325294</v>
@@ -15035,13 +17047,19 @@
       <c r="J382" t="n">
         <v>576</v>
       </c>
+      <c r="K382" t="n">
+        <v>256850.665728479</v>
+      </c>
+      <c r="L382" t="n">
+        <v>0.22425482074043</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B383" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C383" t="n">
         <v>395934</v>
@@ -15067,13 +17085,19 @@
       <c r="J383" t="n">
         <v>564</v>
       </c>
+      <c r="K383" t="n">
+        <v>163654.367620039</v>
+      </c>
+      <c r="L383" t="n">
+        <v>0.344628749114387</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B384" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C384" t="n">
         <v>604962</v>
@@ -15099,13 +17123,19 @@
       <c r="J384" t="n">
         <v>876</v>
       </c>
+      <c r="K384" t="n">
+        <v>266550.259474102</v>
+      </c>
+      <c r="L384" t="n">
+        <v>0.328643461735258</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B385" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C385" t="n">
         <v>206371</v>
@@ -15131,13 +17161,19 @@
       <c r="J385" t="n">
         <v>456</v>
       </c>
+      <c r="K385" t="n">
+        <v>136291.288867412</v>
+      </c>
+      <c r="L385" t="n">
+        <v>0.334577509530788</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C386" t="n">
         <v>464151</v>
@@ -15163,13 +17199,19 @@
       <c r="J386" t="n">
         <v>4140</v>
       </c>
+      <c r="K386" t="n">
+        <v>258563.069997883</v>
+      </c>
+      <c r="L386" t="n">
+        <v>1.60115673132822</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B387" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C387" t="n">
         <v>500004</v>
@@ -15195,13 +17237,19 @@
       <c r="J387" t="n">
         <v>504</v>
       </c>
+      <c r="K387" t="n">
+        <v>212039.642186861</v>
+      </c>
+      <c r="L387" t="n">
+        <v>0.237691402797146</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B388" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C388" t="n">
         <v>134985</v>
@@ -15227,13 +17275,19 @@
       <c r="J388" t="n">
         <v>2268</v>
       </c>
+      <c r="K388" t="n">
+        <v>178793.329111353</v>
+      </c>
+      <c r="L388" t="n">
+        <v>1.26850370272343</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B389" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C389" t="n">
         <v>159805</v>
@@ -15259,13 +17313,19 @@
       <c r="J389" t="n">
         <v>984</v>
       </c>
+      <c r="K389" t="n">
+        <v>329370.206223732</v>
+      </c>
+      <c r="L389" t="n">
+        <v>0.298751976167387</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B390" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C390" t="n">
         <v>96517</v>
@@ -15291,13 +17351,19 @@
       <c r="J390" t="n">
         <v>288</v>
       </c>
+      <c r="K390" t="n">
+        <v>142816.891461631</v>
+      </c>
+      <c r="L390" t="n">
+        <v>0.201656818778593</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B391" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C391" t="n">
         <v>128481</v>
@@ -15323,13 +17389,19 @@
       <c r="J391" t="n">
         <v>588</v>
       </c>
+      <c r="K391" t="n">
+        <v>263438.861849538</v>
+      </c>
+      <c r="L391" t="n">
+        <v>0.223201693125987</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B392" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C392" t="n">
         <v>72040</v>
@@ -15353,13 +17425,19 @@
       <c r="J392" t="n">
         <v>1308</v>
       </c>
+      <c r="K392" t="n">
+        <v>221008.59651827</v>
+      </c>
+      <c r="L392" t="n">
+        <v>0.591832182370279</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B393" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C393" t="n">
         <v>84199</v>
@@ -15385,13 +17463,15 @@
       <c r="J393" t="n">
         <v>1260</v>
       </c>
+      <c r="K393"/>
+      <c r="L393"/>
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B394" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C394" t="n">
         <v>816108</v>
@@ -15417,13 +17497,19 @@
       <c r="J394" t="n">
         <v>1704</v>
       </c>
+      <c r="K394" t="n">
+        <v>283731.267784261</v>
+      </c>
+      <c r="L394" t="n">
+        <v>0.600568281848887</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B395" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C395" t="n">
         <v>104776</v>
@@ -15449,13 +17535,19 @@
       <c r="J395" t="n">
         <v>288</v>
       </c>
+      <c r="K395" t="n">
+        <v>129774.549968442</v>
+      </c>
+      <c r="L395" t="n">
+        <v>0.221923327855913</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B396" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C396" t="n">
         <v>655189</v>
@@ -15481,13 +17573,19 @@
       <c r="J396" t="n">
         <v>2208</v>
       </c>
+      <c r="K396" t="n">
+        <v>232003.729056487</v>
+      </c>
+      <c r="L396" t="n">
+        <v>0.951708840620576</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B397" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C397" t="n">
         <v>92093</v>
@@ -15507,13 +17605,15 @@
       <c r="J397" t="n">
         <v>288</v>
       </c>
+      <c r="K397"/>
+      <c r="L397"/>
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B398" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C398" t="n">
         <v>399098</v>
@@ -15539,13 +17639,19 @@
       <c r="J398" t="n">
         <v>564</v>
       </c>
+      <c r="K398" t="n">
+        <v>180102.210246978</v>
+      </c>
+      <c r="L398" t="n">
+        <v>0.313155512764987</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B399" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C399" t="n">
         <v>3424560</v>
@@ -15571,13 +17677,19 @@
       <c r="J399" t="n">
         <v>1932</v>
       </c>
+      <c r="K399" t="n">
+        <v>237636.319352926</v>
+      </c>
+      <c r="L399" t="n">
+        <v>0.813007037501993</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B400" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C400" t="n">
         <v>166552</v>
@@ -15603,13 +17715,19 @@
       <c r="J400" t="n">
         <v>780</v>
       </c>
+      <c r="K400" t="n">
+        <v>171877.921995811</v>
+      </c>
+      <c r="L400" t="n">
+        <v>0.453810466721263</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B401" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C401" t="n">
         <v>601396</v>
@@ -15635,13 +17753,19 @@
       <c r="J401" t="n">
         <v>1236</v>
       </c>
+      <c r="K401" t="n">
+        <v>201186.246921655</v>
+      </c>
+      <c r="L401" t="n">
+        <v>0.614356109779869</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B402" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C402" t="n">
         <v>232648</v>
@@ -15667,13 +17791,19 @@
       <c r="J402" t="n">
         <v>1896</v>
       </c>
+      <c r="K402" t="n">
+        <v>96732.4844307099</v>
+      </c>
+      <c r="L402" t="n">
+        <v>1.96004476795809</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B403" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C403" t="n">
         <v>114101</v>
@@ -15699,13 +17829,19 @@
       <c r="J403" t="n">
         <v>3072</v>
       </c>
+      <c r="K403" t="n">
+        <v>225478.640220924</v>
+      </c>
+      <c r="L403" t="n">
+        <v>1.36243503907512</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B404" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C404" t="n">
         <v>156634</v>
@@ -15731,13 +17867,19 @@
       <c r="J404" t="n">
         <v>1164</v>
       </c>
+      <c r="K404" t="n">
+        <v>351544.196707608</v>
+      </c>
+      <c r="L404" t="n">
+        <v>0.331110571843159</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B405" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C405" t="n">
         <v>392138</v>
@@ -15763,13 +17905,19 @@
       <c r="J405" t="n">
         <v>2928</v>
       </c>
+      <c r="K405" t="n">
+        <v>314502.031269106</v>
+      </c>
+      <c r="L405" t="n">
+        <v>0.930995576780435</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C406" t="n">
         <v>102195</v>
@@ -15795,13 +17943,19 @@
       <c r="J406" t="n">
         <v>2892</v>
       </c>
+      <c r="K406" t="n">
+        <v>490046.041702992</v>
+      </c>
+      <c r="L406" t="n">
+        <v>0.590148629698103</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B407" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C407" t="n">
         <v>1080149</v>
@@ -15827,13 +17981,19 @@
       <c r="J407" t="n">
         <v>852</v>
       </c>
+      <c r="K407" t="n">
+        <v>222146.621432211</v>
+      </c>
+      <c r="L407" t="n">
+        <v>0.383530478432233</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B408" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C408" t="n">
         <v>67034</v>
@@ -15853,13 +18013,19 @@
       <c r="J408" t="n">
         <v>588</v>
       </c>
+      <c r="K408" t="n">
+        <v>274147.632183772</v>
+      </c>
+      <c r="L408" t="n">
+        <v>0.214482975948463</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B409" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C409" t="n">
         <v>1060423</v>
@@ -15885,13 +18051,19 @@
       <c r="J409" t="n">
         <v>576</v>
       </c>
+      <c r="K409" t="n">
+        <v>121131.750435008</v>
+      </c>
+      <c r="L409" t="n">
+        <v>0.475515294653524</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B410" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C410" t="n">
         <v>132699</v>
@@ -15917,13 +18089,15 @@
       <c r="J410" t="n">
         <v>456</v>
       </c>
+      <c r="K410"/>
+      <c r="L410"/>
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B411" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C411" t="n">
         <v>281081</v>
@@ -15949,13 +18123,19 @@
       <c r="J411" t="n">
         <v>600</v>
       </c>
+      <c r="K411" t="n">
+        <v>217487.627832822</v>
+      </c>
+      <c r="L411" t="n">
+        <v>0.275877761865704</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B412" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C412" t="n">
         <v>121319</v>
@@ -15981,13 +18161,19 @@
       <c r="J412" t="n">
         <v>648</v>
       </c>
+      <c r="K412" t="n">
+        <v>232092.745403931</v>
+      </c>
+      <c r="L412" t="n">
+        <v>0.279198731038417</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B413" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C413" t="n">
         <v>249091</v>
@@ -16013,13 +18199,19 @@
       <c r="J413" t="n">
         <v>816</v>
       </c>
+      <c r="K413" t="n">
+        <v>253273.092640037</v>
+      </c>
+      <c r="L413" t="n">
+        <v>0.322181875498214</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B414" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C414" t="n">
         <v>998747</v>
@@ -16045,13 +18237,19 @@
       <c r="J414" t="n">
         <v>6312</v>
       </c>
+      <c r="K414" t="n">
+        <v>530453.63634485</v>
+      </c>
+      <c r="L414" t="n">
+        <v>1.18992491850815</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C415" t="n">
         <v>153179</v>
@@ -16077,13 +18275,19 @@
       <c r="J415" t="n">
         <v>600</v>
       </c>
+      <c r="K415" t="n">
+        <v>140425.005233602</v>
+      </c>
+      <c r="L415" t="n">
+        <v>0.427274329811759</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B416" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C416" t="n">
         <v>455101</v>
@@ -16109,13 +18313,19 @@
       <c r="J416" t="n">
         <v>2196</v>
       </c>
+      <c r="K416" t="n">
+        <v>356247.566502049</v>
+      </c>
+      <c r="L416" t="n">
+        <v>0.616425263353306</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B417" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C417" t="n">
         <v>98446</v>
@@ -16135,13 +18345,15 @@
       <c r="J417" t="n">
         <v>288</v>
       </c>
+      <c r="K417"/>
+      <c r="L417"/>
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C418" t="n">
         <v>1796689</v>
@@ -16167,13 +18379,19 @@
       <c r="J418" t="n">
         <v>1284</v>
       </c>
+      <c r="K418" t="n">
+        <v>294122.725556231</v>
+      </c>
+      <c r="L418" t="n">
+        <v>0.436552462096141</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B419" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C419" t="n">
         <v>483546</v>
@@ -16199,13 +18417,19 @@
       <c r="J419" t="n">
         <v>1500</v>
       </c>
+      <c r="K419" t="n">
+        <v>253433.557889048</v>
+      </c>
+      <c r="L419" t="n">
+        <v>0.591871105189902</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B420" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C420" t="n">
         <v>305814</v>
@@ -16231,13 +18455,19 @@
       <c r="J420" t="n">
         <v>840</v>
       </c>
+      <c r="K420" t="n">
+        <v>188415.360381597</v>
+      </c>
+      <c r="L420" t="n">
+        <v>0.445823524312854</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B421" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C421" t="n">
         <v>204110</v>
@@ -16263,13 +18493,19 @@
       <c r="J421" t="n">
         <v>312</v>
       </c>
+      <c r="K421" t="n">
+        <v>118869.663146346</v>
+      </c>
+      <c r="L421" t="n">
+        <v>0.262472351432412</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B422" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C422" t="n">
         <v>6437907</v>
@@ -16295,13 +18531,19 @@
       <c r="J422" t="n">
         <v>1596</v>
       </c>
+      <c r="K422" t="n">
+        <v>357937.485625276</v>
+      </c>
+      <c r="L422" t="n">
+        <v>0.445887917330583</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B423" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C423" t="n">
         <v>462220</v>
@@ -16327,13 +18569,15 @@
       <c r="J423" t="n">
         <v>4176</v>
       </c>
+      <c r="K423"/>
+      <c r="L423"/>
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B424" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C424" t="n">
         <v>170081</v>
@@ -16359,13 +18603,19 @@
       <c r="J424" t="n">
         <v>1644</v>
       </c>
+      <c r="K424" t="n">
+        <v>129967.292463979</v>
+      </c>
+      <c r="L424" t="n">
+        <v>1.26493363740392</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B425" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C425" t="n">
         <v>86245</v>
@@ -16391,13 +18641,19 @@
       <c r="J425" t="n">
         <v>288</v>
       </c>
+      <c r="K425" t="n">
+        <v>222059.629663849</v>
+      </c>
+      <c r="L425" t="n">
+        <v>0.129694893410374</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B426" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C426" t="n">
         <v>113140</v>
@@ -16421,13 +18677,15 @@
       <c r="J426" t="n">
         <v>732</v>
       </c>
+      <c r="K426"/>
+      <c r="L426"/>
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B427" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C427" t="n">
         <v>139091</v>
@@ -16453,13 +18711,19 @@
       <c r="J427" t="n">
         <v>2844</v>
       </c>
+      <c r="K427" t="n">
+        <v>191998.943048657</v>
+      </c>
+      <c r="L427" t="n">
+        <v>1.48125815425935</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B428" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C428" t="n">
         <v>112738</v>
@@ -16485,13 +18749,19 @@
       <c r="J428" t="n">
         <v>2004</v>
       </c>
+      <c r="K428" t="n">
+        <v>177325.054920071</v>
+      </c>
+      <c r="L428" t="n">
+        <v>1.13012794548593</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B429" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C429" t="n">
         <v>127023</v>
@@ -16517,13 +18787,19 @@
       <c r="J429" t="n">
         <v>516</v>
       </c>
+      <c r="K429" t="n">
+        <v>331694.057796173</v>
+      </c>
+      <c r="L429" t="n">
+        <v>0.155565041902886</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B430" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C430" t="n">
         <v>106029</v>
@@ -16549,13 +18825,19 @@
       <c r="J430" t="n">
         <v>1884</v>
       </c>
+      <c r="K430" t="n">
+        <v>317546.790875249</v>
+      </c>
+      <c r="L430" t="n">
+        <v>0.593298390705558</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C431" t="n">
         <v>661217</v>
@@ -16581,13 +18863,19 @@
       <c r="J431" t="n">
         <v>588</v>
       </c>
+      <c r="K431" t="n">
+        <v>150638.663848613</v>
+      </c>
+      <c r="L431" t="n">
+        <v>0.390338034723225</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B432" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C432" t="n">
         <v>149869</v>
@@ -16613,13 +18901,15 @@
       <c r="J432" t="n">
         <v>684</v>
       </c>
+      <c r="K432"/>
+      <c r="L432"/>
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B433" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C433" t="n">
         <v>154693</v>
@@ -16639,13 +18929,19 @@
       <c r="J433" t="n">
         <v>2184</v>
       </c>
+      <c r="K433" t="n">
+        <v>247200.777864138</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0.883492365546007</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B434" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C434" t="n">
         <v>113236</v>
@@ -16671,13 +18967,15 @@
       <c r="J434" t="n">
         <v>2100</v>
       </c>
+      <c r="K434"/>
+      <c r="L434"/>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B435" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C435" t="n">
         <v>480522</v>
@@ -16703,13 +19001,19 @@
       <c r="J435" t="n">
         <v>1284</v>
       </c>
+      <c r="K435" t="n">
+        <v>398901.187727181</v>
+      </c>
+      <c r="L435" t="n">
+        <v>0.321884225844462</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B436" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C436" t="n">
         <v>148005</v>
@@ -16735,13 +19039,19 @@
       <c r="J436" t="n">
         <v>828</v>
       </c>
+      <c r="K436" t="n">
+        <v>236973.654979978</v>
+      </c>
+      <c r="L436" t="n">
+        <v>0.349405928718092</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B437" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C437" t="n">
         <v>705187</v>
@@ -16767,13 +19077,19 @@
       <c r="J437" t="n">
         <v>696</v>
       </c>
+      <c r="K437" t="n">
+        <v>165186.424229886</v>
+      </c>
+      <c r="L437" t="n">
+        <v>0.421342131016405</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B438" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C438" t="n">
         <v>73943</v>
@@ -16795,13 +19111,15 @@
       <c r="J438" t="n">
         <v>1764</v>
       </c>
+      <c r="K438"/>
+      <c r="L438"/>
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B439" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C439" t="n">
         <v>116632</v>
@@ -16827,13 +19145,15 @@
       <c r="J439" t="n">
         <v>1728</v>
       </c>
+      <c r="K439"/>
+      <c r="L439"/>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B440" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C440" t="n">
         <v>881248</v>
@@ -16859,13 +19179,19 @@
       <c r="J440" t="n">
         <v>4380</v>
       </c>
+      <c r="K440" t="n">
+        <v>348346.526893311</v>
+      </c>
+      <c r="L440" t="n">
+        <v>1.25736864353508</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B441" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C441" t="n">
         <v>258523</v>
@@ -16891,13 +19217,19 @@
       <c r="J441" t="n">
         <v>1740</v>
       </c>
+      <c r="K441" t="n">
+        <v>279856.142124253</v>
+      </c>
+      <c r="L441" t="n">
+        <v>0.621748011958036</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B442" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C442" t="n">
         <v>471240</v>
@@ -16923,13 +19255,19 @@
       <c r="J442" t="n">
         <v>624</v>
       </c>
+      <c r="K442" t="n">
+        <v>223323.153165479</v>
+      </c>
+      <c r="L442" t="n">
+        <v>0.279415721637078</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B443" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C443" t="n">
         <v>426086</v>
@@ -16955,13 +19293,19 @@
       <c r="J443" t="n">
         <v>2544</v>
       </c>
+      <c r="K443" t="n">
+        <v>201283.887717361</v>
+      </c>
+      <c r="L443" t="n">
+        <v>1.26388655786112</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B444" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C444" t="n">
         <v>220310</v>
@@ -16986,6 +19330,12 @@
       </c>
       <c r="J444" t="n">
         <v>768</v>
+      </c>
+      <c r="K444" t="n">
+        <v>206313.733398038</v>
+      </c>
+      <c r="L444" t="n">
+        <v>0.372248607666999</v>
       </c>
     </row>
   </sheetData>
